--- a/data.xlsx
+++ b/data.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9681ED5-38F2-43D5-BE75-D597D075FB48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEEEADCE-EB1E-4BB9-8483-2948955FE1D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Theo dõi HĐ_Chi tiết" sheetId="2" r:id="rId1"/>
@@ -388,6 +388,73 @@
     <author>Author</author>
   </authors>
   <commentList>
+    <comment ref="C4" authorId="0" shapeId="0" xr:uid="{CD469296-9AB6-4AF1-9FCD-9E36120E8AC2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">
+Giảm 30% so giá 8.3tr ban đầu</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C15" authorId="0" shapeId="0" xr:uid="{4598195B-FDD6-44BA-9BF1-359D336871E1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">
+Giảm 20% so với giá ban đầu 11.5tr</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C20" authorId="0" shapeId="0" xr:uid="{E4FD0575-78F2-4181-A6E3-64113CF2CB76}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">
+Giảm 20% so với giá thuê ban đầu 10tr/tháng
+</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="H55" authorId="0" shapeId="0" xr:uid="{E338F18C-7E52-4B19-A114-941D13F6C257}">
       <text>
         <r>
@@ -505,7 +572,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3380" uniqueCount="1251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3500" uniqueCount="1299">
   <si>
     <t>filter</t>
   </si>
@@ -4563,7 +4630,151 @@
     <t>22HGV004_HGV228</t>
   </si>
   <si>
-    <t>22HTD009_HTD297</t>
+    <t>HCM2026-1395</t>
+  </si>
+  <si>
+    <t>Góc Marie Curie - William Sharkespeare, Đường Marie Cuire, Phường Đông Hòa, TP.HCM</t>
+  </si>
+  <si>
+    <t>Có_HCM2026-1395</t>
+  </si>
+  <si>
+    <t>A Cường_GĐ TT XTĐT DHQG</t>
+  </si>
+  <si>
+    <t>Chưa có thông tin</t>
+  </si>
+  <si>
+    <t>……../2026/HĐTMB/IPSC-DKV</t>
+  </si>
+  <si>
+    <t>Có_HCM2026-1451</t>
+  </si>
+  <si>
+    <t>HCM2022-172</t>
+  </si>
+  <si>
+    <t>HCM2022-PTM-003</t>
+  </si>
+  <si>
+    <t>HCM2022-PTM-004</t>
+  </si>
+  <si>
+    <t>HCM2024-023</t>
+  </si>
+  <si>
+    <t>HCM2024-022</t>
+  </si>
+  <si>
+    <t>HCM2023-PTM-024</t>
+  </si>
+  <si>
+    <t>HCM2022-PTM-002</t>
+  </si>
+  <si>
+    <t>32/HĐ2025.TCSHT-VTCC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94/HĐ.TCSHT-TTVTHM.2025 </t>
+  </si>
+  <si>
+    <t>93/HĐ.TCSHT-TTVTHM.2025</t>
+  </si>
+  <si>
+    <t>122-2025/HĐ.TCSHT/VNPT.HCM</t>
+  </si>
+  <si>
+    <t>150-2025/HĐ.TCSHT/VNPT.HCM</t>
+  </si>
+  <si>
+    <t>91/HĐ.TCSHT-TTVTHM.2025</t>
+  </si>
+  <si>
+    <t>92/HĐ.TCSHT-TTVTHM.2025</t>
+  </si>
+  <si>
+    <t>22/08/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26/9/2025 </t>
+  </si>
+  <si>
+    <t>26/9/2025</t>
+  </si>
+  <si>
+    <t>26/11/2025</t>
+  </si>
+  <si>
+    <t>24HHM108</t>
+  </si>
+  <si>
+    <t>343-25/TT.MLMN-ĐVTT</t>
+  </si>
+  <si>
+    <t>HCMSHH27</t>
+  </si>
+  <si>
+    <t>71-2026/HĐ-MBF.HCM-VTĐ</t>
+  </si>
+  <si>
+    <t>26HBC053</t>
+  </si>
+  <si>
+    <t>933/HĐ-VTT</t>
+  </si>
+  <si>
+    <t>15/04/2026 - 15/10/2026</t>
+  </si>
+  <si>
+    <t>01/07/2026 - 31/12/2026</t>
+  </si>
+  <si>
+    <t>01/07/2026 - 30/09/2026</t>
+  </si>
+  <si>
+    <t>01/05/2026 - 30/11/2026</t>
+  </si>
+  <si>
+    <t>01/09/2026 - 28/02/2027</t>
+  </si>
+  <si>
+    <t>chưa nhận tiền</t>
+  </si>
+  <si>
+    <t>01/05/2026 - 31/10/2026</t>
+  </si>
+  <si>
+    <t>14/09/2026</t>
+  </si>
+  <si>
+    <t>Dự kiến thanh toán kỳ đầu tiên</t>
+  </si>
+  <si>
+    <t>Có_HCMSHH27</t>
+  </si>
+  <si>
+    <t>HCM2026-1401</t>
+  </si>
+  <si>
+    <t>948-2026/HD.TCSHT/VNPT.11CM</t>
+  </si>
+  <si>
+    <t>3/6/2026</t>
+  </si>
+  <si>
+    <t>1025-2026/HĐ.TCSHT/VNPT.HCM</t>
+  </si>
+  <si>
+    <t>???</t>
+  </si>
+  <si>
+    <t>HCM2026-1451</t>
+  </si>
+  <si>
+    <t>991-2026/HD.TCS11T/VNPT.HCM</t>
+  </si>
+  <si>
+    <t>17/7/2026</t>
   </si>
 </sst>
 </file>
@@ -4574,7 +4785,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="42" x14ac:knownFonts="1">
+  <fonts count="48" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4852,6 +5063,45 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF00B050"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="163"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF7030A0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="163"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="17">
     <fill>
@@ -5052,7 +5302,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="285">
+  <cellXfs count="302">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5865,6 +6115,49 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="46" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="11" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -7158,7 +7451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AS102"/>
+  <dimension ref="A1:AS103"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" customWidth="1"/>
@@ -7324,39 +7617,39 @@
     <row r="2" spans="1:45" s="100" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="150">
         <f t="shared" ref="A2:AQ2" si="0">SUBTOTAL(3,A4:A190)</f>
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B2" s="150">
         <f t="shared" si="0"/>
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C2" s="150">
         <f t="shared" si="0"/>
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D2" s="150">
         <f t="shared" si="0"/>
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E2" s="150">
         <f t="shared" si="0"/>
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F2" s="150">
         <f t="shared" si="0"/>
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G2" s="150">
         <f t="shared" si="0"/>
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H2" s="150">
         <f t="shared" si="0"/>
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I2" s="150">
         <f t="shared" si="0"/>
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J2" s="150">
         <f t="shared" ref="J2:L2" si="1">SUBTOTAL(3,J4:J190)</f>
@@ -7424,11 +7717,11 @@
       </c>
       <c r="Z2" s="150">
         <f t="shared" si="0"/>
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AA2" s="150">
         <f t="shared" si="0"/>
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AB2" s="270"/>
       <c r="AC2" s="150">
@@ -7437,15 +7730,15 @@
       </c>
       <c r="AD2" s="150">
         <f t="shared" si="0"/>
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AE2" s="150">
         <f t="shared" si="0"/>
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AF2" s="150">
         <f t="shared" si="0"/>
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG2" s="150">
         <f t="shared" si="0"/>
@@ -7453,7 +7746,7 @@
       </c>
       <c r="AH2" s="150">
         <f t="shared" si="0"/>
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AI2" s="150">
         <f t="shared" si="0"/>
@@ -7461,27 +7754,27 @@
       </c>
       <c r="AJ2" s="150">
         <f t="shared" si="0"/>
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK2" s="150">
         <f t="shared" si="0"/>
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AL2" s="150">
         <f t="shared" si="0"/>
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AM2" s="150">
         <f t="shared" si="0"/>
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AN2" s="150">
         <f t="shared" si="0"/>
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AO2" s="150">
         <f t="shared" si="0"/>
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AP2" s="150">
         <f t="shared" si="0"/>
@@ -7489,7 +7782,7 @@
       </c>
       <c r="AQ2" s="150">
         <f t="shared" si="0"/>
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AR2" s="151"/>
     </row>
@@ -12484,8 +12777,8 @@
       <c r="H51" s="27" t="s">
         <v>893</v>
       </c>
-      <c r="I51" s="25" t="s">
-        <v>893</v>
+      <c r="I51" s="34" t="s">
+        <v>1290</v>
       </c>
       <c r="J51" s="20">
         <v>45078</v>
@@ -14459,8 +14752,8 @@
       <c r="G72" s="34" t="s">
         <v>353</v>
       </c>
-      <c r="H72" s="27" t="s">
-        <v>893</v>
+      <c r="H72" s="34" t="s">
+        <v>1256</v>
       </c>
       <c r="I72" s="25" t="s">
         <v>893</v>
@@ -16772,8 +17065,8 @@
       <c r="H97" s="34" t="s">
         <v>1227</v>
       </c>
-      <c r="I97" s="25" t="s">
-        <v>893</v>
+      <c r="I97" s="34" t="s">
+        <v>1227</v>
       </c>
       <c r="J97" s="20">
         <v>45738</v>
@@ -17310,6 +17603,95 @@
       <c r="AP102" s="48"/>
       <c r="AQ102">
         <v>2025</v>
+      </c>
+    </row>
+    <row r="103" spans="1:44" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A103" s="4">
+        <v>100</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D103" s="2">
+        <v>106.799272</v>
+      </c>
+      <c r="E103" s="2">
+        <v>10.878826</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>1251</v>
+      </c>
+      <c r="G103" s="27" t="s">
+        <v>893</v>
+      </c>
+      <c r="H103" s="34" t="s">
+        <v>1252</v>
+      </c>
+      <c r="I103" s="25" t="s">
+        <v>893</v>
+      </c>
+      <c r="J103" s="20"/>
+      <c r="K103" s="20"/>
+      <c r="L103" s="20"/>
+      <c r="M103" s="34"/>
+      <c r="N103" s="97"/>
+      <c r="O103" s="48"/>
+      <c r="P103" s="97"/>
+      <c r="Q103" s="97"/>
+      <c r="R103" s="48"/>
+      <c r="S103" s="48"/>
+      <c r="T103" s="48"/>
+      <c r="U103" s="48"/>
+      <c r="V103" s="48"/>
+      <c r="W103" s="48"/>
+      <c r="X103" s="48"/>
+      <c r="Y103" s="48"/>
+      <c r="Z103" s="2" t="s">
+        <v>1253</v>
+      </c>
+      <c r="AA103" s="101">
+        <v>8000000</v>
+      </c>
+      <c r="AB103" s="101"/>
+      <c r="AC103" s="101"/>
+      <c r="AD103" s="95">
+        <v>0</v>
+      </c>
+      <c r="AE103" s="101">
+        <v>0</v>
+      </c>
+      <c r="AF103" s="101">
+        <v>13500000</v>
+      </c>
+      <c r="AG103" s="87"/>
+      <c r="AH103" s="111" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI103" s="118"/>
+      <c r="AJ103" s="42" t="s">
+        <v>1254</v>
+      </c>
+      <c r="AK103" s="2" t="s">
+        <v>1254</v>
+      </c>
+      <c r="AL103" s="41" t="s">
+        <v>1254</v>
+      </c>
+      <c r="AM103" s="2" t="s">
+        <v>1255</v>
+      </c>
+      <c r="AN103" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO103" s="2">
+        <v>30</v>
+      </c>
+      <c r="AP103" s="48"/>
+      <c r="AQ103">
+        <v>2026</v>
       </c>
     </row>
   </sheetData>
@@ -20741,7 +21123,7 @@
       </c>
       <c r="AJ4" s="169">
         <f ca="1">AC4-TODAY()</f>
-        <v>-125</v>
+        <v>-142</v>
       </c>
       <c r="AK4" s="170">
         <f>3*D4</f>
@@ -20878,7 +21260,7 @@
       </c>
       <c r="AJ5" s="179">
         <f ca="1">AD5-TODAY()</f>
-        <v>-90</v>
+        <v>-107</v>
       </c>
       <c r="AK5" s="173">
         <f>3*D5</f>
@@ -21015,7 +21397,7 @@
       </c>
       <c r="AJ6" s="169">
         <f ca="1">AB6-TODAY()</f>
-        <v>-126</v>
+        <v>-143</v>
       </c>
       <c r="AK6" s="170">
         <f>3*D6</f>
@@ -21152,7 +21534,7 @@
       </c>
       <c r="AJ7" s="179">
         <f ca="1">T7-TODAY()</f>
-        <v>-155</v>
+        <v>-172</v>
       </c>
       <c r="AK7" s="173">
         <f>6*D7</f>
@@ -21289,7 +21671,7 @@
       </c>
       <c r="AJ8" s="186">
         <f ca="1">AB8-TODAY()</f>
-        <v>-95</v>
+        <v>-112</v>
       </c>
       <c r="AK8" s="164">
         <f>3*D8</f>
@@ -21426,7 +21808,7 @@
       </c>
       <c r="AJ9" s="169">
         <f ca="1">AB9-TODAY()</f>
-        <v>-111</v>
+        <v>-128</v>
       </c>
       <c r="AK9" s="164">
         <f>3*D9</f>
@@ -21563,7 +21945,7 @@
       </c>
       <c r="AJ10" s="169">
         <f ca="1">AB10-TODAY()</f>
-        <v>-155</v>
+        <v>-172</v>
       </c>
       <c r="AK10" s="164">
         <f>D10*3</f>
@@ -21700,7 +22082,7 @@
       </c>
       <c r="AJ11" s="169">
         <f ca="1">AB11-TODAY()</f>
-        <v>-162</v>
+        <v>-179</v>
       </c>
       <c r="AK11" s="187">
         <f>D11*3</f>
@@ -21837,7 +22219,7 @@
       </c>
       <c r="AJ12" s="169">
         <f ca="1">AA12-TODAY()</f>
-        <v>-155</v>
+        <v>-172</v>
       </c>
       <c r="AK12" s="164">
         <f>3*D12</f>
@@ -21974,7 +22356,7 @@
       </c>
       <c r="AJ13" s="169">
         <f ca="1">AB13-TODAY()</f>
-        <v>-154</v>
+        <v>-171</v>
       </c>
       <c r="AK13" s="164">
         <f>3*7000000</f>
@@ -22111,7 +22493,7 @@
       </c>
       <c r="AJ14" s="186">
         <f ca="1">AA14-TODAY()</f>
-        <v>-145</v>
+        <v>-162</v>
       </c>
       <c r="AK14" s="164">
         <f>3*D14</f>
@@ -22248,7 +22630,7 @@
       </c>
       <c r="AJ15" s="186">
         <f ca="1">T15-TODAY()</f>
-        <v>-14</v>
+        <v>-31</v>
       </c>
       <c r="AK15" s="164">
         <f>6*D15</f>
@@ -22384,7 +22766,7 @@
       </c>
       <c r="AJ16" s="169">
         <f ca="1">T16-TODAY()</f>
-        <v>-101</v>
+        <v>-118</v>
       </c>
       <c r="AK16" s="164">
         <f>6*D16</f>
@@ -22525,7 +22907,7 @@
       </c>
       <c r="AJ17" s="186">
         <f ca="1">AB17-TODAY()</f>
-        <v>-94</v>
+        <v>-111</v>
       </c>
       <c r="AK17" s="164">
         <f>3*D17</f>
@@ -22662,7 +23044,7 @@
       </c>
       <c r="AJ18" s="186">
         <f ca="1">T18-TODAY()</f>
-        <v>-80</v>
+        <v>-97</v>
       </c>
       <c r="AK18" s="164">
         <f>6*D18</f>
@@ -22799,7 +23181,7 @@
       </c>
       <c r="AJ19" s="186">
         <f ca="1">AA19-TODAY()</f>
-        <v>-114</v>
+        <v>-131</v>
       </c>
       <c r="AK19" s="164">
         <f>3*D19</f>
@@ -22936,7 +23318,7 @@
       </c>
       <c r="AJ20" s="192">
         <f ca="1">T20-TODAY()</f>
-        <v>-2</v>
+        <v>-19</v>
       </c>
       <c r="AK20" s="173">
         <f>6*D20</f>
@@ -23073,7 +23455,7 @@
       </c>
       <c r="AJ21" s="186">
         <f ca="1">AB21-TODAY()</f>
-        <v>-90</v>
+        <v>-107</v>
       </c>
       <c r="AK21" s="164">
         <f>3*D21</f>
@@ -23210,7 +23592,7 @@
       </c>
       <c r="AJ22" s="186">
         <f ca="1">T22-TODAY()</f>
-        <v>-26</v>
+        <v>-43</v>
       </c>
       <c r="AK22" s="164">
         <f>6*D22</f>
@@ -23347,7 +23729,7 @@
       </c>
       <c r="AJ23" s="186">
         <f ca="1">T23-TODAY()</f>
-        <v>-26</v>
+        <v>-43</v>
       </c>
       <c r="AK23" s="164">
         <f>D23*6</f>
@@ -23484,7 +23866,7 @@
       </c>
       <c r="AJ24" s="186">
         <f ca="1">Z24-TODAY()</f>
-        <v>-73</v>
+        <v>-90</v>
       </c>
       <c r="AK24" s="187">
         <f>3*D24</f>
@@ -23621,7 +24003,7 @@
       </c>
       <c r="AJ25" s="192">
         <f ca="1">AA25-TODAY()</f>
-        <v>-111</v>
+        <v>-128</v>
       </c>
       <c r="AK25" s="173">
         <f>3*D25</f>
@@ -23758,7 +24140,7 @@
       </c>
       <c r="AJ26" s="186">
         <f ca="1">S26-TODAY()</f>
-        <v>-155</v>
+        <v>-172</v>
       </c>
       <c r="AK26" s="164">
         <f>6*D26</f>
@@ -23895,7 +24277,7 @@
       </c>
       <c r="AJ27" s="186">
         <f ca="1">AA27-TODAY()</f>
-        <v>-125</v>
+        <v>-142</v>
       </c>
       <c r="AK27" s="164">
         <f>3*D27</f>
@@ -24032,7 +24414,7 @@
       </c>
       <c r="AJ28" s="192">
         <f ca="1">T28-TODAY()</f>
-        <v>-79</v>
+        <v>-96</v>
       </c>
       <c r="AK28" s="173">
         <f>6*D28</f>
@@ -24167,7 +24549,7 @@
       </c>
       <c r="AJ29" s="186">
         <f ca="1">U29-TODAY()</f>
-        <v>-64</v>
+        <v>-81</v>
       </c>
       <c r="AK29" s="201">
         <f>D29*6</f>
@@ -24304,7 +24686,7 @@
       </c>
       <c r="AJ30" s="186">
         <f ca="1">Z30-TODAY()</f>
-        <v>-121</v>
+        <v>-138</v>
       </c>
       <c r="AK30" s="201">
         <f>D30*3</f>
@@ -24441,7 +24823,7 @@
       </c>
       <c r="AJ31" s="192">
         <f ca="1">T31-TODAY()</f>
-        <v>7</v>
+        <v>-10</v>
       </c>
       <c r="AK31" s="194">
         <f>D31*6</f>
@@ -24578,7 +24960,7 @@
       </c>
       <c r="AJ32" s="186">
         <f ca="1">Z32-TODAY()</f>
-        <v>-85</v>
+        <v>-102</v>
       </c>
       <c r="AK32" s="201">
         <f t="shared" ref="AK32:AK36" si="41">D32*3</f>
@@ -24715,7 +25097,7 @@
       </c>
       <c r="AJ33" s="186">
         <f ca="1">Z33-TODAY()</f>
-        <v>-128</v>
+        <v>-145</v>
       </c>
       <c r="AK33" s="205">
         <f t="shared" si="41"/>
@@ -24852,7 +25234,7 @@
       </c>
       <c r="AJ34" s="192">
         <f ca="1">Z34-TODAY()</f>
-        <v>-101</v>
+        <v>-118</v>
       </c>
       <c r="AK34" s="194">
         <f t="shared" si="41"/>
@@ -24989,7 +25371,7 @@
       </c>
       <c r="AJ35" s="186">
         <f ca="1">Z35-TODAY()</f>
-        <v>-95</v>
+        <v>-112</v>
       </c>
       <c r="AK35" s="201">
         <f t="shared" si="41"/>
@@ -25126,7 +25508,7 @@
       </c>
       <c r="AJ36" s="186">
         <f ca="1">Z36-TODAY()</f>
-        <v>-95</v>
+        <v>-112</v>
       </c>
       <c r="AK36" s="201">
         <f t="shared" si="41"/>
@@ -25262,7 +25644,7 @@
       </c>
       <c r="AJ37" s="186">
         <f ca="1">S37-TODAY()</f>
-        <v>-94</v>
+        <v>-111</v>
       </c>
       <c r="AK37" s="201">
         <f>D37*6</f>
@@ -25399,7 +25781,7 @@
       </c>
       <c r="AJ38" s="186">
         <f ca="1">S38-TODAY()</f>
-        <v>-94</v>
+        <v>-111</v>
       </c>
       <c r="AK38" s="201">
         <f>D38*6</f>
@@ -25536,7 +25918,7 @@
       </c>
       <c r="AJ39" s="186">
         <f ca="1">S39-TODAY()</f>
-        <v>-80</v>
+        <v>-97</v>
       </c>
       <c r="AK39" s="201">
         <f>D39*6</f>
@@ -25673,7 +26055,7 @@
       </c>
       <c r="AJ40" s="186">
         <f ca="1">Z40-TODAY()</f>
-        <v>-80</v>
+        <v>-97</v>
       </c>
       <c r="AK40" s="201">
         <f>D40*3</f>
@@ -25810,7 +26192,7 @@
       </c>
       <c r="AJ41" s="186">
         <f ca="1">Y41-TODAY()</f>
-        <v>-162</v>
+        <v>-179</v>
       </c>
       <c r="AK41" s="201">
         <f>D41*3</f>
@@ -25947,7 +26329,7 @@
       </c>
       <c r="AJ42" s="186">
         <f ca="1">X42-TODAY()</f>
-        <v>-125</v>
+        <v>-142</v>
       </c>
       <c r="AK42" s="201">
         <f t="shared" ref="AK42:AK43" si="50">D42*3</f>
@@ -26084,7 +26466,7 @@
       </c>
       <c r="AJ43" s="192">
         <f ca="1">X43-TODAY()</f>
-        <v>-111</v>
+        <v>-128</v>
       </c>
       <c r="AK43" s="194">
         <f t="shared" si="50"/>
@@ -26218,7 +26600,7 @@
       </c>
       <c r="AJ44" s="186">
         <f ca="1">U44-TODAY()</f>
-        <v>-125</v>
+        <v>-142</v>
       </c>
       <c r="AK44" s="201">
         <f>D44*6</f>
@@ -26355,7 +26737,7 @@
       </c>
       <c r="AJ45" s="192">
         <f ca="1">R45-TODAY()</f>
-        <v>7</v>
+        <v>-10</v>
       </c>
       <c r="AK45" s="194">
         <f>D45*6</f>
@@ -26492,7 +26874,7 @@
       </c>
       <c r="AJ46" s="186">
         <f ca="1">Y46-TODAY()</f>
-        <v>-141</v>
+        <v>-158</v>
       </c>
       <c r="AK46" s="201">
         <f>D46*1</f>
@@ -26629,7 +27011,7 @@
       </c>
       <c r="AJ47" s="186">
         <f ca="1">R47-TODAY()</f>
-        <v>-19</v>
+        <v>-36</v>
       </c>
       <c r="AK47" s="201">
         <v>24000000</v>
@@ -26765,7 +27147,7 @@
       </c>
       <c r="AJ48" s="186">
         <f ca="1">R48-TODAY()</f>
-        <v>-19</v>
+        <v>-36</v>
       </c>
       <c r="AK48" s="201">
         <v>24000000</v>
@@ -26901,7 +27283,7 @@
       </c>
       <c r="AJ49" s="186">
         <f ca="1">R49-TODAY()</f>
-        <v>-3</v>
+        <v>-20</v>
       </c>
       <c r="AK49" s="201">
         <f>D49*6</f>
@@ -27038,7 +27420,7 @@
       </c>
       <c r="AJ50" s="186">
         <f t="shared" ref="AJ50:AJ54" ca="1" si="57">Q50-TODAY()</f>
-        <v>-125</v>
+        <v>-142</v>
       </c>
       <c r="AK50" s="201">
         <f>D50*6</f>
@@ -27175,7 +27557,7 @@
       </c>
       <c r="AJ51" s="186">
         <f t="shared" ca="1" si="57"/>
-        <v>-43</v>
+        <v>-60</v>
       </c>
       <c r="AK51" s="194">
         <f t="shared" ref="AK51:AK60" si="58">D51*6</f>
@@ -27312,7 +27694,7 @@
       </c>
       <c r="AJ52" s="186">
         <f t="shared" ca="1" si="57"/>
-        <v>-64</v>
+        <v>-81</v>
       </c>
       <c r="AK52" s="201">
         <f>D52*6</f>
@@ -27449,7 +27831,7 @@
       </c>
       <c r="AJ53" s="186">
         <f t="shared" ca="1" si="57"/>
-        <v>-68</v>
+        <v>-85</v>
       </c>
       <c r="AK53" s="201">
         <f t="shared" si="58"/>
@@ -27586,7 +27968,7 @@
       </c>
       <c r="AJ54" s="186">
         <f t="shared" ca="1" si="57"/>
-        <v>-69</v>
+        <v>-86</v>
       </c>
       <c r="AK54" s="201">
         <f t="shared" si="58"/>
@@ -27723,7 +28105,7 @@
       </c>
       <c r="AJ55" s="186">
         <f ca="1">R55-TODAY()</f>
-        <v>-33</v>
+        <v>-50</v>
       </c>
       <c r="AK55" s="201">
         <f t="shared" si="58"/>
@@ -27860,7 +28242,7 @@
       </c>
       <c r="AJ56" s="186">
         <f t="shared" ref="AJ56:AJ67" ca="1" si="60">P56-TODAY()</f>
-        <v>-159</v>
+        <v>-176</v>
       </c>
       <c r="AK56" s="201">
         <f t="shared" si="58"/>
@@ -27997,7 +28379,7 @@
       </c>
       <c r="AJ57" s="186">
         <f t="shared" ca="1" si="60"/>
-        <v>-146</v>
+        <v>-163</v>
       </c>
       <c r="AK57" s="201">
         <f t="shared" si="58"/>
@@ -28134,7 +28516,7 @@
       </c>
       <c r="AJ58" s="186">
         <f ca="1">Q58-TODAY()</f>
-        <v>2</v>
+        <v>-15</v>
       </c>
       <c r="AK58" s="201">
         <f t="shared" si="58"/>
@@ -28271,7 +28653,7 @@
       </c>
       <c r="AJ59" s="186">
         <f t="shared" ca="1" si="60"/>
-        <v>-125</v>
+        <v>-142</v>
       </c>
       <c r="AK59" s="201">
         <f t="shared" si="58"/>
@@ -28408,7 +28790,7 @@
       </c>
       <c r="AJ60" s="186">
         <f t="shared" ca="1" si="60"/>
-        <v>-125</v>
+        <v>-142</v>
       </c>
       <c r="AK60" s="201">
         <f t="shared" si="58"/>
@@ -28545,7 +28927,7 @@
       </c>
       <c r="AJ61" s="186">
         <f t="shared" ca="1" si="60"/>
-        <v>-134</v>
+        <v>-151</v>
       </c>
       <c r="AK61" s="201">
         <f>D61*6</f>
@@ -28682,7 +29064,7 @@
       </c>
       <c r="AJ62" s="186">
         <f t="shared" ca="1" si="60"/>
-        <v>-89</v>
+        <v>-106</v>
       </c>
       <c r="AK62" s="201">
         <f t="shared" ref="AK62:AK85" si="63">D62*6</f>
@@ -28819,7 +29201,7 @@
       </c>
       <c r="AJ63" s="186">
         <f t="shared" ca="1" si="60"/>
-        <v>-80</v>
+        <v>-97</v>
       </c>
       <c r="AK63" s="201">
         <f t="shared" si="63"/>
@@ -28956,7 +29338,7 @@
       </c>
       <c r="AJ64" s="186">
         <f t="shared" ca="1" si="60"/>
-        <v>-85</v>
+        <v>-102</v>
       </c>
       <c r="AK64" s="201">
         <f>D64*6</f>
@@ -29093,7 +29475,7 @@
       </c>
       <c r="AJ65" s="186">
         <f t="shared" ca="1" si="60"/>
-        <v>-75</v>
+        <v>-92</v>
       </c>
       <c r="AK65" s="201">
         <f t="shared" si="63"/>
@@ -29230,7 +29612,7 @@
       </c>
       <c r="AJ66" s="186">
         <f t="shared" ca="1" si="60"/>
-        <v>-55</v>
+        <v>-72</v>
       </c>
       <c r="AK66" s="201">
         <f>D66*6</f>
@@ -29367,7 +29749,7 @@
       </c>
       <c r="AJ67" s="186">
         <f t="shared" ca="1" si="60"/>
-        <v>-47</v>
+        <v>-64</v>
       </c>
       <c r="AK67" s="201">
         <f t="shared" si="63"/>
@@ -29504,7 +29886,7 @@
       </c>
       <c r="AJ68" s="186">
         <f ca="1">P68-TODAY()</f>
-        <v>7</v>
+        <v>-10</v>
       </c>
       <c r="AK68" s="201">
         <f t="shared" si="63"/>
@@ -29644,7 +30026,7 @@
       </c>
       <c r="AJ69" s="186">
         <f ca="1">P69-TODAY()</f>
-        <v>-2</v>
+        <v>-19</v>
       </c>
       <c r="AK69" s="201">
         <f t="shared" si="63"/>
@@ -29781,7 +30163,7 @@
       </c>
       <c r="AJ70" s="186">
         <f t="shared" ref="AJ70:AJ73" ca="1" si="66">O70-TODAY()</f>
-        <v>-138</v>
+        <v>-155</v>
       </c>
       <c r="AK70" s="201">
         <f t="shared" si="63"/>
@@ -29918,7 +30300,7 @@
       </c>
       <c r="AJ71" s="186">
         <f ca="1">P71-TODAY()</f>
-        <v>-8</v>
+        <v>-25</v>
       </c>
       <c r="AK71" s="201">
         <f t="shared" si="63"/>
@@ -30055,7 +30437,7 @@
       </c>
       <c r="AJ72" s="186">
         <f t="shared" ca="1" si="66"/>
-        <v>-100</v>
+        <v>-117</v>
       </c>
       <c r="AK72" s="201">
         <f t="shared" si="63"/>
@@ -30192,7 +30574,7 @@
       </c>
       <c r="AJ73" s="186">
         <f t="shared" ca="1" si="66"/>
-        <v>-82</v>
+        <v>-99</v>
       </c>
       <c r="AK73" s="201">
         <f t="shared" si="63"/>
@@ -30329,7 +30711,7 @@
       </c>
       <c r="AJ74" s="186">
         <f ca="1">O74-TODAY()</f>
-        <v>-45</v>
+        <v>-62</v>
       </c>
       <c r="AK74" s="201">
         <f t="shared" si="63"/>
@@ -30466,7 +30848,7 @@
       </c>
       <c r="AJ75" s="186">
         <f ca="1">O75-TODAY()</f>
-        <v>-39</v>
+        <v>-56</v>
       </c>
       <c r="AK75" s="201">
         <f t="shared" si="63"/>
@@ -30603,7 +30985,7 @@
       </c>
       <c r="AJ76" s="186">
         <f ca="1">O76-TODAY()</f>
-        <v>-47</v>
+        <v>-64</v>
       </c>
       <c r="AK76" s="201">
         <f t="shared" si="63"/>
@@ -30740,7 +31122,7 @@
       </c>
       <c r="AJ77" s="186">
         <f ca="1">O77-TODAY()</f>
-        <v>-17</v>
+        <v>-34</v>
       </c>
       <c r="AK77" s="201">
         <f t="shared" si="63"/>
@@ -30881,7 +31263,7 @@
       </c>
       <c r="AJ78" s="186">
         <f t="shared" ref="AJ78:AJ79" ca="1" si="67">N78-TODAY()</f>
-        <v>-104</v>
+        <v>-121</v>
       </c>
       <c r="AK78" s="201">
         <f t="shared" si="63"/>
@@ -31018,7 +31400,7 @@
       </c>
       <c r="AJ79" s="186">
         <f t="shared" ca="1" si="67"/>
-        <v>-99</v>
+        <v>-116</v>
       </c>
       <c r="AK79" s="201">
         <f t="shared" si="63"/>
@@ -31155,7 +31537,7 @@
       </c>
       <c r="AJ80" s="186">
         <f ca="1">N80-TODAY()</f>
-        <v>-46</v>
+        <v>-63</v>
       </c>
       <c r="AK80" s="201">
         <f t="shared" si="63"/>
@@ -31292,7 +31674,7 @@
       </c>
       <c r="AJ81" s="186">
         <f ca="1">N81-TODAY()</f>
-        <v>-33</v>
+        <v>-50</v>
       </c>
       <c r="AK81" s="201">
         <f t="shared" si="63"/>
@@ -31429,7 +31811,7 @@
       </c>
       <c r="AJ82" s="186">
         <f ca="1">N82-TODAY()</f>
-        <v>-57</v>
+        <v>-74</v>
       </c>
       <c r="AK82" s="201">
         <f t="shared" si="63"/>
@@ -31566,7 +31948,7 @@
       </c>
       <c r="AJ83" s="186">
         <f ca="1">N83-TODAY()</f>
-        <v>-56</v>
+        <v>-73</v>
       </c>
       <c r="AK83" s="201">
         <f t="shared" si="63"/>
@@ -31703,7 +32085,7 @@
       </c>
       <c r="AJ84" s="186">
         <f ca="1">N84-TODAY()</f>
-        <v>2</v>
+        <v>-15</v>
       </c>
       <c r="AK84" s="201">
         <f t="shared" si="63"/>
@@ -31840,7 +32222,7 @@
       </c>
       <c r="AJ85" s="186">
         <f ca="1">M85-TODAY()</f>
-        <v>-155</v>
+        <v>-172</v>
       </c>
       <c r="AK85" s="201">
         <f t="shared" si="63"/>
@@ -33020,7 +33402,7 @@
       </c>
       <c r="Z2" s="230">
         <f>SUBTOTAL(9,Z4:Z199)</f>
-        <v>4846680000</v>
+        <v>4815900000</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.3">
@@ -33110,8 +33492,8 @@
       <c r="B4" s="163" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="187">
-        <v>6640000</v>
+      <c r="C4" s="225">
+        <v>5810000</v>
       </c>
       <c r="D4" s="187"/>
       <c r="E4" s="162" t="s">
@@ -33198,7 +33580,7 @@
       </c>
       <c r="Z4" s="201">
         <f t="shared" ref="Z4:Z17" si="11">C4*6</f>
-        <v>39840000</v>
+        <v>34860000</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.3">
@@ -34190,8 +34572,8 @@
       <c r="B15" s="163" t="s">
         <v>415</v>
       </c>
-      <c r="C15" s="187">
-        <v>11500000</v>
+      <c r="C15" s="225">
+        <v>9200000</v>
       </c>
       <c r="D15" s="187"/>
       <c r="E15" s="162" t="s">
@@ -34278,7 +34660,7 @@
       </c>
       <c r="Z15" s="201">
         <f t="shared" si="11"/>
-        <v>69000000</v>
+        <v>55200000</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.3">
@@ -34682,8 +35064,8 @@
       <c r="B20" s="163" t="s">
         <v>313</v>
       </c>
-      <c r="C20" s="187">
-        <v>10000000</v>
+      <c r="C20" s="225">
+        <v>8000000</v>
       </c>
       <c r="D20" s="187"/>
       <c r="E20" s="162" t="s">
@@ -34770,7 +35152,7 @@
       </c>
       <c r="Z20" s="201">
         <f t="shared" si="13"/>
-        <v>60000000</v>
+        <v>48000000</v>
       </c>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.3">
@@ -41742,7 +42124,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99A93212-344E-4288-8D1E-646D88DABF7E}">
-  <dimension ref="A1:AG12"/>
+  <dimension ref="A1:AG22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.44140625" customWidth="1"/>
@@ -41861,33 +42243,33 @@
       <c r="A2" s="223"/>
       <c r="B2" s="223">
         <f>SUBTOTAL(3,B4:B50)</f>
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C2" s="223">
         <f>SUBTOTAL(3,C4:C50)</f>
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D2" s="223"/>
       <c r="E2" s="223"/>
       <c r="F2" s="223">
         <f t="shared" ref="F2:X2" si="0">SUBTOTAL(3,F4:F50)</f>
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="G2" s="223">
         <f t="shared" ref="G2" si="1">SUBTOTAL(3,G4:G50)</f>
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="H2" s="223">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I2" s="223">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J2" s="223">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="K2" s="223">
         <f t="shared" si="0"/>
@@ -43175,6 +43557,326 @@
         <v>16500000</v>
       </c>
       <c r="AG12" s="17"/>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A13" s="224" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B13" s="285" t="s">
+        <v>392</v>
+      </c>
+      <c r="C13" s="285" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D13" s="285" t="s">
+        <v>1264</v>
+      </c>
+      <c r="E13" s="286" t="s">
+        <v>1271</v>
+      </c>
+      <c r="F13" s="287">
+        <v>5830000</v>
+      </c>
+      <c r="G13" s="224" t="s">
+        <v>77</v>
+      </c>
+      <c r="H13" s="299">
+        <v>46107</v>
+      </c>
+      <c r="I13" s="300" t="s">
+        <v>778</v>
+      </c>
+      <c r="J13" s="300" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A14" s="224">
+        <v>11</v>
+      </c>
+      <c r="B14" s="285" t="s">
+        <v>415</v>
+      </c>
+      <c r="C14" s="285" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D14" s="285" t="s">
+        <v>1265</v>
+      </c>
+      <c r="E14" s="286" t="s">
+        <v>1272</v>
+      </c>
+      <c r="F14" s="287">
+        <v>4682700</v>
+      </c>
+      <c r="G14" s="224" t="s">
+        <v>77</v>
+      </c>
+      <c r="H14" s="299">
+        <v>46066</v>
+      </c>
+      <c r="I14" s="300" t="s">
+        <v>778</v>
+      </c>
+      <c r="J14" s="300" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A15" s="224">
+        <v>12</v>
+      </c>
+      <c r="B15" s="285" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C15" s="285" t="s">
+        <v>1259</v>
+      </c>
+      <c r="D15" s="285" t="s">
+        <v>1266</v>
+      </c>
+      <c r="E15" s="286" t="s">
+        <v>1273</v>
+      </c>
+      <c r="F15" s="287">
+        <v>7700000</v>
+      </c>
+      <c r="G15" s="224" t="s">
+        <v>77</v>
+      </c>
+      <c r="H15" s="299">
+        <v>46114</v>
+      </c>
+      <c r="I15" s="300" t="s">
+        <v>778</v>
+      </c>
+      <c r="J15" s="300" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A16" s="224">
+        <v>13</v>
+      </c>
+      <c r="B16" s="285" t="s">
+        <v>420</v>
+      </c>
+      <c r="C16" s="285" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D16" s="285" t="s">
+        <v>1267</v>
+      </c>
+      <c r="E16" s="286" t="s">
+        <v>1274</v>
+      </c>
+      <c r="F16" s="287">
+        <v>6500000</v>
+      </c>
+      <c r="G16" s="224" t="s">
+        <v>77</v>
+      </c>
+      <c r="H16" s="299">
+        <v>46107</v>
+      </c>
+      <c r="I16" s="300" t="s">
+        <v>778</v>
+      </c>
+      <c r="J16" s="300" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="224">
+        <v>14</v>
+      </c>
+      <c r="B17" s="285" t="s">
+        <v>251</v>
+      </c>
+      <c r="C17" s="285" t="s">
+        <v>1261</v>
+      </c>
+      <c r="D17" s="285" t="s">
+        <v>1268</v>
+      </c>
+      <c r="E17" s="286" t="s">
+        <v>1274</v>
+      </c>
+      <c r="F17" s="287">
+        <v>6600000</v>
+      </c>
+      <c r="G17" s="224" t="s">
+        <v>77</v>
+      </c>
+      <c r="H17" s="299">
+        <v>46108</v>
+      </c>
+      <c r="I17" s="300" t="s">
+        <v>778</v>
+      </c>
+      <c r="J17" s="300" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="224">
+        <v>15</v>
+      </c>
+      <c r="B18" s="285" t="s">
+        <v>195</v>
+      </c>
+      <c r="C18" s="285" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D18" s="285" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E18" s="286" t="s">
+        <v>1273</v>
+      </c>
+      <c r="F18" s="287">
+        <v>5577000</v>
+      </c>
+      <c r="G18" s="224" t="s">
+        <v>77</v>
+      </c>
+      <c r="H18" s="299">
+        <v>46010</v>
+      </c>
+      <c r="I18" s="300" t="s">
+        <v>778</v>
+      </c>
+      <c r="J18" s="300" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" s="224">
+        <v>16</v>
+      </c>
+      <c r="B19" s="285" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="285" t="s">
+        <v>1263</v>
+      </c>
+      <c r="D19" s="285" t="s">
+        <v>1270</v>
+      </c>
+      <c r="E19" s="286" t="s">
+        <v>1273</v>
+      </c>
+      <c r="F19" s="287">
+        <v>4943400</v>
+      </c>
+      <c r="G19" s="224" t="s">
+        <v>77</v>
+      </c>
+      <c r="H19" s="299">
+        <v>46010</v>
+      </c>
+      <c r="I19" s="300" t="s">
+        <v>778</v>
+      </c>
+      <c r="J19" s="300" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="224">
+        <v>17</v>
+      </c>
+      <c r="B20" s="285" t="s">
+        <v>809</v>
+      </c>
+      <c r="C20" s="285" t="s">
+        <v>1291</v>
+      </c>
+      <c r="D20" s="285" t="s">
+        <v>1292</v>
+      </c>
+      <c r="E20" s="286" t="s">
+        <v>1293</v>
+      </c>
+      <c r="F20" s="287">
+        <v>8778000</v>
+      </c>
+      <c r="G20" s="224" t="s">
+        <v>77</v>
+      </c>
+      <c r="H20" s="301" t="s">
+        <v>778</v>
+      </c>
+      <c r="I20" s="300" t="s">
+        <v>778</v>
+      </c>
+      <c r="J20" s="300" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="224">
+        <v>18</v>
+      </c>
+      <c r="B21" s="285" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C21" s="285" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D21" s="285" t="s">
+        <v>1294</v>
+      </c>
+      <c r="E21" s="301" t="s">
+        <v>1295</v>
+      </c>
+      <c r="F21" s="287">
+        <v>13500000</v>
+      </c>
+      <c r="G21" s="224" t="s">
+        <v>77</v>
+      </c>
+      <c r="H21" s="301" t="s">
+        <v>778</v>
+      </c>
+      <c r="I21" s="300" t="s">
+        <v>778</v>
+      </c>
+      <c r="J21" s="300" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="224">
+        <v>19</v>
+      </c>
+      <c r="B22" s="285" t="s">
+        <v>743</v>
+      </c>
+      <c r="C22" s="285" t="s">
+        <v>1296</v>
+      </c>
+      <c r="D22" s="285" t="s">
+        <v>1297</v>
+      </c>
+      <c r="E22" s="286" t="s">
+        <v>1298</v>
+      </c>
+      <c r="F22" s="287">
+        <v>7000000</v>
+      </c>
+      <c r="G22" s="224" t="s">
+        <v>77</v>
+      </c>
+      <c r="H22" s="301" t="s">
+        <v>778</v>
+      </c>
+      <c r="I22" s="300" t="s">
+        <v>778</v>
+      </c>
+      <c r="J22" s="300" t="s">
+        <v>778</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="30" type="noConversion"/>
@@ -43184,7 +43886,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5C27CFB-57FF-4B3C-845A-AF9FA2575408}">
-  <dimension ref="A1:Y12"/>
+  <dimension ref="A1:AA16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.44140625" customWidth="1"/>
@@ -43201,7 +43903,7 @@
     <col min="25" max="25" width="15.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="61.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" ht="61.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="223" t="s">
         <v>24</v>
       </c>
@@ -43278,23 +43980,23 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" s="41"/>
       <c r="B2" s="41">
         <f t="shared" ref="B2:T2" si="0">SUBTOTAL(3,B4:B49)</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C2" s="41">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D2" s="41">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E2" s="41">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F2" s="41">
         <f>SUBTOTAL(3,F4:F49)</f>
@@ -43303,78 +44005,78 @@
       <c r="G2" s="41"/>
       <c r="H2" s="41">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I2" s="41">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J2" s="41">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K2" s="41">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L2" s="41">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M2" s="41">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N2" s="41">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O2" s="41">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P2" s="41">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q2" s="41">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R2" s="41">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="S2" s="41">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T2" s="41">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="U2" s="41">
         <f t="shared" ref="U2:X2" si="1">SUBTOTAL(3,U4:U49)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="V2" s="41">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W2" s="41">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="X2" s="41">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Y2" s="247">
         <f>SUBTOTAL(9,Y4:Y49)</f>
-        <v>347220000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+        <v>470820000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" s="224"/>
       <c r="B3" s="41" t="s">
         <v>0</v>
@@ -43447,7 +44149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" s="224">
         <v>1</v>
       </c>
@@ -43536,8 +44238,11 @@
         <f>I4*H4</f>
         <v>39000000</v>
       </c>
-    </row>
-    <row r="5" spans="1:25" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="Z4" s="295" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A5" s="224">
         <v>2</v>
       </c>
@@ -43626,8 +44331,11 @@
         <f t="shared" ref="Y5:Y6" si="7">I5*H5</f>
         <v>33000000</v>
       </c>
-    </row>
-    <row r="6" spans="1:25" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="Z5" s="296" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A6" s="224">
         <v>3</v>
       </c>
@@ -43717,8 +44425,11 @@
         <f t="shared" si="7"/>
         <v>42000000</v>
       </c>
-    </row>
-    <row r="7" spans="1:25" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="Z6" s="296" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A7" s="224">
         <v>4</v>
       </c>
@@ -43809,8 +44520,11 @@
         <f>I7*H7</f>
         <v>19500000</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="Z7" s="296" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A8" s="224">
         <v>5</v>
       </c>
@@ -43844,7 +44558,7 @@
         <v>45809</v>
       </c>
       <c r="L8" s="249">
-        <f t="shared" ref="L8:T12" si="13">EDATE(K8,6)</f>
+        <f t="shared" ref="L8:T14" si="13">EDATE(K8,6)</f>
         <v>45992</v>
       </c>
       <c r="M8" s="249">
@@ -43884,23 +44598,26 @@
         <v>47635</v>
       </c>
       <c r="V8" s="249">
-        <f t="shared" ref="V8:V12" si="15">EDATE(U8,6)</f>
+        <f t="shared" ref="V8:V14" si="15">EDATE(U8,6)</f>
         <v>47818</v>
       </c>
       <c r="W8" s="249">
-        <f t="shared" ref="W8:W12" si="16">EDATE(V8,6)</f>
+        <f t="shared" ref="W8:W14" si="16">EDATE(V8,6)</f>
         <v>48000</v>
       </c>
       <c r="X8" s="249">
-        <f t="shared" ref="X8:X12" si="17">EDATE(W8,6)</f>
+        <f t="shared" ref="X8:X14" si="17">EDATE(W8,6)</f>
         <v>48183</v>
       </c>
       <c r="Y8" s="227">
         <f>H8*6</f>
         <v>40920000.000000007</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="Z8" s="296" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A9" s="224">
         <v>6</v>
       </c>
@@ -43908,7 +44625,7 @@
         <v>251</v>
       </c>
       <c r="C9" s="224" t="s">
-        <v>1250</v>
+        <v>1113</v>
       </c>
       <c r="D9" s="41" t="s">
         <v>1114</v>
@@ -43932,66 +44649,68 @@
         <v>45915</v>
       </c>
       <c r="K9" s="250">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="L9" s="226">
-        <f t="shared" si="13"/>
-        <v>46296</v>
+        <v>46357</v>
       </c>
       <c r="M9" s="226">
         <f t="shared" si="13"/>
-        <v>46478</v>
+        <v>46539</v>
       </c>
       <c r="N9" s="226">
         <f t="shared" si="13"/>
-        <v>46661</v>
+        <v>46722</v>
       </c>
       <c r="O9" s="226">
         <f t="shared" si="13"/>
-        <v>46844</v>
+        <v>46905</v>
       </c>
       <c r="P9" s="226">
         <f t="shared" si="13"/>
-        <v>47027</v>
+        <v>47088</v>
       </c>
       <c r="Q9" s="226">
         <f t="shared" si="13"/>
-        <v>47209</v>
+        <v>47270</v>
       </c>
       <c r="R9" s="226">
         <f t="shared" si="13"/>
-        <v>47392</v>
+        <v>47453</v>
       </c>
       <c r="S9" s="226">
         <f t="shared" si="13"/>
-        <v>47574</v>
+        <v>47635</v>
       </c>
       <c r="T9" s="226">
         <f t="shared" si="13"/>
-        <v>47757</v>
+        <v>47818</v>
       </c>
       <c r="U9" s="226">
         <f t="shared" si="14"/>
-        <v>47939</v>
+        <v>48000</v>
       </c>
       <c r="V9" s="226">
         <f t="shared" si="15"/>
-        <v>48122</v>
+        <v>48183</v>
       </c>
       <c r="W9" s="226">
         <f t="shared" si="16"/>
-        <v>48305</v>
+        <v>48366</v>
       </c>
       <c r="X9" s="226">
         <f t="shared" si="17"/>
-        <v>48488</v>
+        <v>48549</v>
       </c>
       <c r="Y9" s="227">
-        <f t="shared" ref="Y9:Y12" si="18">H9*6</f>
+        <f t="shared" ref="Y9:Y15" si="18">H9*6</f>
         <v>42000000</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="Z9" s="296" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A10" s="224">
         <v>7</v>
       </c>
@@ -44008,7 +44727,7 @@
         <v>1119</v>
       </c>
       <c r="F10" s="224"/>
-      <c r="G10" s="41" t="s">
+      <c r="G10" s="290" t="s">
         <v>1117</v>
       </c>
       <c r="H10" s="254">
@@ -44017,68 +44736,75 @@
       <c r="I10" s="224">
         <v>6</v>
       </c>
-      <c r="J10" s="249"/>
-      <c r="K10" s="249">
+      <c r="J10" s="249" t="s">
+        <v>785</v>
+      </c>
+      <c r="K10" s="250">
         <v>46023</v>
       </c>
       <c r="L10" s="226">
-        <f t="shared" si="13"/>
-        <v>46204</v>
+        <v>46266</v>
       </c>
       <c r="M10" s="226">
         <f t="shared" si="13"/>
-        <v>46388</v>
+        <v>46447</v>
       </c>
       <c r="N10" s="226">
         <f t="shared" si="13"/>
-        <v>46569</v>
+        <v>46631</v>
       </c>
       <c r="O10" s="226">
         <f t="shared" si="13"/>
-        <v>46753</v>
+        <v>46813</v>
       </c>
       <c r="P10" s="226">
         <f t="shared" si="13"/>
-        <v>46935</v>
+        <v>46997</v>
       </c>
       <c r="Q10" s="226">
         <f t="shared" si="13"/>
-        <v>47119</v>
+        <v>47178</v>
       </c>
       <c r="R10" s="226">
         <f t="shared" si="13"/>
-        <v>47300</v>
+        <v>47362</v>
       </c>
       <c r="S10" s="226">
         <f t="shared" si="13"/>
-        <v>47484</v>
+        <v>47543</v>
       </c>
       <c r="T10" s="226">
         <f t="shared" si="13"/>
-        <v>47665</v>
+        <v>47727</v>
       </c>
       <c r="U10" s="226">
-        <f t="shared" si="14"/>
-        <v>47849</v>
+        <f t="shared" ref="U10:U14" si="19">EDATE(T10,6)</f>
+        <v>47908</v>
       </c>
       <c r="V10" s="226">
         <f t="shared" si="15"/>
-        <v>48030</v>
+        <v>48092</v>
       </c>
       <c r="W10" s="226">
         <f t="shared" si="16"/>
-        <v>48214</v>
+        <v>48274</v>
       </c>
       <c r="X10" s="226">
         <f t="shared" si="17"/>
-        <v>48396</v>
+        <v>48458</v>
       </c>
       <c r="Y10" s="227">
         <f t="shared" si="18"/>
         <v>48000000</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="Z10" s="296" t="s">
+        <v>1285</v>
+      </c>
+      <c r="AA10" s="91" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A11" s="224">
         <v>8</v>
       </c>
@@ -44095,7 +44821,7 @@
         <v>1119</v>
       </c>
       <c r="F11" s="224"/>
-      <c r="G11" s="41" t="s">
+      <c r="G11" s="290" t="s">
         <v>1121</v>
       </c>
       <c r="H11" s="254">
@@ -44104,68 +44830,75 @@
       <c r="I11" s="224">
         <v>6</v>
       </c>
-      <c r="J11" s="249"/>
-      <c r="K11" s="249">
+      <c r="J11" s="249" t="s">
+        <v>785</v>
+      </c>
+      <c r="K11" s="250">
         <v>46023</v>
       </c>
       <c r="L11" s="226">
-        <f t="shared" si="13"/>
-        <v>46204</v>
+        <v>46266</v>
       </c>
       <c r="M11" s="226">
         <f t="shared" si="13"/>
-        <v>46388</v>
+        <v>46447</v>
       </c>
       <c r="N11" s="226">
         <f t="shared" si="13"/>
-        <v>46569</v>
+        <v>46631</v>
       </c>
       <c r="O11" s="226">
         <f t="shared" si="13"/>
-        <v>46753</v>
+        <v>46813</v>
       </c>
       <c r="P11" s="226">
         <f t="shared" si="13"/>
-        <v>46935</v>
+        <v>46997</v>
       </c>
       <c r="Q11" s="226">
         <f t="shared" si="13"/>
-        <v>47119</v>
+        <v>47178</v>
       </c>
       <c r="R11" s="226">
         <f t="shared" si="13"/>
-        <v>47300</v>
+        <v>47362</v>
       </c>
       <c r="S11" s="226">
         <f t="shared" si="13"/>
-        <v>47484</v>
+        <v>47543</v>
       </c>
       <c r="T11" s="226">
         <f t="shared" si="13"/>
-        <v>47665</v>
+        <v>47727</v>
       </c>
       <c r="U11" s="226">
-        <f t="shared" si="14"/>
-        <v>47849</v>
+        <f t="shared" si="19"/>
+        <v>47908</v>
       </c>
       <c r="V11" s="226">
         <f t="shared" si="15"/>
-        <v>48030</v>
+        <v>48092</v>
       </c>
       <c r="W11" s="226">
         <f t="shared" si="16"/>
-        <v>48214</v>
+        <v>48274</v>
       </c>
       <c r="X11" s="226">
         <f t="shared" si="17"/>
-        <v>48396</v>
+        <v>48458</v>
       </c>
       <c r="Y11" s="227">
         <f t="shared" si="18"/>
         <v>44400000</v>
       </c>
-    </row>
-    <row r="12" spans="1:25" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="Z11" s="296" t="s">
+        <v>1285</v>
+      </c>
+      <c r="AA11" s="91" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A12" s="224">
         <v>9</v>
       </c>
@@ -44182,7 +44915,7 @@
         <v>1119</v>
       </c>
       <c r="F12" s="224"/>
-      <c r="G12" s="41" t="s">
+      <c r="G12" s="290" t="s">
         <v>1123</v>
       </c>
       <c r="H12" s="254">
@@ -44191,66 +44924,313 @@
       <c r="I12" s="224">
         <v>6</v>
       </c>
-      <c r="J12" s="249"/>
-      <c r="K12" s="249">
+      <c r="J12" s="249" t="s">
+        <v>785</v>
+      </c>
+      <c r="K12" s="250">
         <v>46023</v>
       </c>
       <c r="L12" s="226">
-        <f t="shared" si="13"/>
-        <v>46204</v>
+        <v>46266</v>
       </c>
       <c r="M12" s="226">
         <f t="shared" si="13"/>
-        <v>46388</v>
+        <v>46447</v>
       </c>
       <c r="N12" s="226">
         <f t="shared" si="13"/>
-        <v>46569</v>
+        <v>46631</v>
       </c>
       <c r="O12" s="226">
         <f t="shared" si="13"/>
-        <v>46753</v>
+        <v>46813</v>
       </c>
       <c r="P12" s="226">
         <f t="shared" si="13"/>
-        <v>46935</v>
+        <v>46997</v>
       </c>
       <c r="Q12" s="226">
         <f t="shared" si="13"/>
-        <v>47119</v>
+        <v>47178</v>
       </c>
       <c r="R12" s="226">
         <f t="shared" si="13"/>
-        <v>47300</v>
+        <v>47362</v>
       </c>
       <c r="S12" s="226">
         <f t="shared" si="13"/>
-        <v>47484</v>
+        <v>47543</v>
       </c>
       <c r="T12" s="226">
         <f t="shared" si="13"/>
-        <v>47665</v>
+        <v>47727</v>
       </c>
       <c r="U12" s="226">
-        <f t="shared" si="14"/>
-        <v>47849</v>
+        <f t="shared" si="19"/>
+        <v>47908</v>
       </c>
       <c r="V12" s="226">
         <f t="shared" si="15"/>
-        <v>48030</v>
+        <v>48092</v>
       </c>
       <c r="W12" s="226">
         <f t="shared" si="16"/>
-        <v>48214</v>
+        <v>48274</v>
       </c>
       <c r="X12" s="226">
         <f t="shared" si="17"/>
-        <v>48396</v>
+        <v>48458</v>
       </c>
       <c r="Y12" s="227">
         <f t="shared" si="18"/>
         <v>38400000</v>
       </c>
+      <c r="Z12" s="296" t="s">
+        <v>1285</v>
+      </c>
+      <c r="AA12" s="91" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="288">
+        <v>10</v>
+      </c>
+      <c r="B13" s="41" t="s">
+        <v>723</v>
+      </c>
+      <c r="C13" s="224" t="s">
+        <v>1275</v>
+      </c>
+      <c r="D13" s="41" t="s">
+        <v>1276</v>
+      </c>
+      <c r="E13" s="289">
+        <v>45890</v>
+      </c>
+      <c r="F13" s="224"/>
+      <c r="G13" s="224" t="s">
+        <v>1275</v>
+      </c>
+      <c r="H13" s="254">
+        <v>5600000</v>
+      </c>
+      <c r="I13" s="224">
+        <v>6</v>
+      </c>
+      <c r="J13" s="249" t="s">
+        <v>785</v>
+      </c>
+      <c r="K13" s="249">
+        <v>46143</v>
+      </c>
+      <c r="L13" s="249">
+        <f t="shared" ref="L13:L16" si="20">EDATE(K13,6)</f>
+        <v>46327</v>
+      </c>
+      <c r="M13" s="249">
+        <f t="shared" si="13"/>
+        <v>46508</v>
+      </c>
+      <c r="N13" s="249">
+        <f t="shared" si="13"/>
+        <v>46692</v>
+      </c>
+      <c r="O13" s="249">
+        <f t="shared" si="13"/>
+        <v>46874</v>
+      </c>
+      <c r="P13" s="249">
+        <f t="shared" si="13"/>
+        <v>47058</v>
+      </c>
+      <c r="Q13" s="249">
+        <f t="shared" si="13"/>
+        <v>47239</v>
+      </c>
+      <c r="R13" s="249">
+        <f t="shared" si="13"/>
+        <v>47423</v>
+      </c>
+      <c r="S13" s="249">
+        <f t="shared" si="13"/>
+        <v>47604</v>
+      </c>
+      <c r="T13" s="249">
+        <f t="shared" si="13"/>
+        <v>47788</v>
+      </c>
+      <c r="U13" s="249">
+        <f t="shared" si="19"/>
+        <v>47969</v>
+      </c>
+      <c r="V13" s="249">
+        <f t="shared" si="15"/>
+        <v>48153</v>
+      </c>
+      <c r="W13" s="249">
+        <f t="shared" si="16"/>
+        <v>48335</v>
+      </c>
+      <c r="X13" s="249">
+        <f t="shared" si="17"/>
+        <v>48519</v>
+      </c>
+      <c r="Y13" s="227">
+        <f t="shared" si="18"/>
+        <v>33600000</v>
+      </c>
+      <c r="Z13" s="296" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="224">
+        <v>11</v>
+      </c>
+      <c r="B14" s="41" t="s">
+        <v>571</v>
+      </c>
+      <c r="C14" s="224" t="s">
+        <v>1277</v>
+      </c>
+      <c r="D14" s="41" t="s">
+        <v>1278</v>
+      </c>
+      <c r="E14" s="289">
+        <v>46223</v>
+      </c>
+      <c r="F14" s="224"/>
+      <c r="G14" s="224" t="s">
+        <v>1277</v>
+      </c>
+      <c r="H14" s="254">
+        <v>8500000</v>
+      </c>
+      <c r="I14" s="224">
+        <v>6</v>
+      </c>
+      <c r="J14" s="249" t="s">
+        <v>785</v>
+      </c>
+      <c r="K14" s="249">
+        <v>46279</v>
+      </c>
+      <c r="L14" s="249">
+        <f t="shared" si="20"/>
+        <v>46460</v>
+      </c>
+      <c r="M14" s="249">
+        <f t="shared" si="13"/>
+        <v>46644</v>
+      </c>
+      <c r="N14" s="249">
+        <f t="shared" si="13"/>
+        <v>46826</v>
+      </c>
+      <c r="O14" s="249">
+        <f t="shared" si="13"/>
+        <v>47010</v>
+      </c>
+      <c r="P14" s="249">
+        <f t="shared" si="13"/>
+        <v>47191</v>
+      </c>
+      <c r="Q14" s="249">
+        <f t="shared" si="13"/>
+        <v>47375</v>
+      </c>
+      <c r="R14" s="249">
+        <f t="shared" si="13"/>
+        <v>47556</v>
+      </c>
+      <c r="S14" s="249">
+        <f t="shared" si="13"/>
+        <v>47740</v>
+      </c>
+      <c r="T14" s="249">
+        <f t="shared" si="13"/>
+        <v>47921</v>
+      </c>
+      <c r="U14" s="249">
+        <f t="shared" si="19"/>
+        <v>48105</v>
+      </c>
+      <c r="V14" s="249">
+        <f t="shared" si="15"/>
+        <v>48287</v>
+      </c>
+      <c r="W14" s="249">
+        <f t="shared" si="16"/>
+        <v>48471</v>
+      </c>
+      <c r="X14" s="249">
+        <f t="shared" si="17"/>
+        <v>48652</v>
+      </c>
+      <c r="Y14" s="227">
+        <f t="shared" si="18"/>
+        <v>51000000</v>
+      </c>
+      <c r="Z14" s="297" t="s">
+        <v>1288</v>
+      </c>
+      <c r="AA14" s="298" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A15" s="288">
+        <v>12</v>
+      </c>
+      <c r="B15" s="291" t="s">
+        <v>809</v>
+      </c>
+      <c r="C15" s="292" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D15" s="291" t="s">
+        <v>1280</v>
+      </c>
+      <c r="E15" s="293">
+        <v>46234</v>
+      </c>
+      <c r="F15" s="224"/>
+      <c r="G15" s="292" t="s">
+        <v>1279</v>
+      </c>
+      <c r="H15" s="294">
+        <v>6500000</v>
+      </c>
+      <c r="I15" s="224">
+        <v>6</v>
+      </c>
+      <c r="J15" s="249" t="s">
+        <v>785</v>
+      </c>
+      <c r="K15" s="249" t="s">
+        <v>785</v>
+      </c>
+      <c r="L15" s="249"/>
+      <c r="M15" s="249"/>
+      <c r="N15" s="249"/>
+      <c r="O15" s="249"/>
+      <c r="P15" s="249"/>
+      <c r="Q15" s="249"/>
+      <c r="R15" s="249"/>
+      <c r="S15" s="249"/>
+      <c r="T15" s="249"/>
+      <c r="U15" s="227"/>
+      <c r="Y15" s="227">
+        <f t="shared" si="18"/>
+        <v>39000000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B16" s="37"/>
+      <c r="D16" s="37"/>
+      <c r="E16" s="37"/>
+      <c r="G16" s="37"/>
     </row>
   </sheetData>
   <phoneticPr fontId="30" type="noConversion"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98C03354-C26E-4162-8414-92DCEE82DC16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10E1A5F5-D99A-4A2F-953E-1CEA964236EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Theo dõi HĐ_Chi tiết" sheetId="2" r:id="rId1"/>
@@ -6149,6 +6149,9 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6168,9 +6171,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -12831,8 +12831,8 @@
       <c r="AD51" s="95">
         <v>7000000</v>
       </c>
-      <c r="AE51" s="101">
-        <v>0</v>
+      <c r="AE51" s="254">
+        <v>8500000</v>
       </c>
       <c r="AF51" s="154">
         <v>0</v>
@@ -12842,7 +12842,7 @@
         <v>79</v>
       </c>
       <c r="AI51" s="118"/>
-      <c r="AJ51" s="302" t="s">
+      <c r="AJ51" s="295" t="s">
         <v>1297</v>
       </c>
       <c r="AK51" s="117" t="s">
@@ -18501,10 +18501,10 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="20.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A5" s="295" t="s">
+      <c r="A5" s="296" t="s">
         <v>662</v>
       </c>
-      <c r="B5" s="296"/>
+      <c r="B5" s="297"/>
       <c r="C5" s="146">
         <f>SUM(C2:C4)</f>
         <v>9</v>
@@ -20186,7 +20186,7 @@
         <v>24000000</v>
       </c>
       <c r="E3" s="76"/>
-      <c r="F3" s="297" t="s">
+      <c r="F3" s="298" t="s">
         <v>266</v>
       </c>
     </row>
@@ -20202,7 +20202,7 @@
         <v>11000000</v>
       </c>
       <c r="E4" s="76"/>
-      <c r="F4" s="298"/>
+      <c r="F4" s="299"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B5" s="75">
@@ -20216,7 +20216,7 @@
         <v>18600000</v>
       </c>
       <c r="E5" s="76"/>
-      <c r="F5" s="298"/>
+      <c r="F5" s="299"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6" s="70">
@@ -20231,7 +20231,7 @@
       <c r="E6" s="71" t="s">
         <v>275</v>
       </c>
-      <c r="F6" s="298"/>
+      <c r="F6" s="299"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" s="75">
@@ -20245,7 +20245,7 @@
         <v>18000000</v>
       </c>
       <c r="E7" s="76"/>
-      <c r="F7" s="298"/>
+      <c r="F7" s="299"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="70">
@@ -20260,7 +20260,7 @@
       <c r="E8" s="71" t="s">
         <v>275</v>
       </c>
-      <c r="F8" s="298"/>
+      <c r="F8" s="299"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="70">
@@ -20275,7 +20275,7 @@
       <c r="E9" s="71" t="s">
         <v>275</v>
       </c>
-      <c r="F9" s="298"/>
+      <c r="F9" s="299"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="70">
@@ -20290,7 +20290,7 @@
       <c r="E10" s="71" t="s">
         <v>275</v>
       </c>
-      <c r="F10" s="298"/>
+      <c r="F10" s="299"/>
     </row>
     <row r="11" spans="2:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="B11" s="55"/>
@@ -20302,7 +20302,7 @@
         <v>535239920</v>
       </c>
       <c r="E11" s="72"/>
-      <c r="F11" s="298"/>
+      <c r="F11" s="299"/>
       <c r="J11"/>
     </row>
     <row r="12" spans="2:10" hidden="1" x14ac:dyDescent="0.3">
@@ -20316,7 +20316,7 @@
         <v>5786705</v>
       </c>
       <c r="E12" s="73"/>
-      <c r="F12" s="298"/>
+      <c r="F12" s="299"/>
     </row>
     <row r="13" spans="2:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="B13" s="60">
@@ -20330,7 +20330,7 @@
         <v>18900000</v>
       </c>
       <c r="E13" s="74"/>
-      <c r="F13" s="299"/>
+      <c r="F13" s="300"/>
     </row>
     <row r="14" spans="2:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="B14" s="60"/>
@@ -32749,20 +32749,20 @@
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
-      <c r="L1" s="300" t="s">
+      <c r="L1" s="301" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="300"/>
-      <c r="N1" s="300"/>
-      <c r="O1" s="300"/>
-      <c r="P1" s="300"/>
-      <c r="Q1" s="301" t="s">
+      <c r="M1" s="301"/>
+      <c r="N1" s="301"/>
+      <c r="O1" s="301"/>
+      <c r="P1" s="301"/>
+      <c r="Q1" s="302" t="s">
         <v>2</v>
       </c>
-      <c r="R1" s="301"/>
-      <c r="S1" s="301"/>
-      <c r="T1" s="301"/>
-      <c r="U1" s="301"/>
+      <c r="R1" s="302"/>
+      <c r="S1" s="302"/>
+      <c r="T1" s="302"/>
+      <c r="U1" s="302"/>
     </row>
     <row r="2" spans="1:22" ht="48" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -45192,7 +45192,7 @@
         <v>48652</v>
       </c>
       <c r="Y14" s="227">
-        <f t="shared" si="18"/>
+        <f>H14*6</f>
         <v>51000000</v>
       </c>
       <c r="Z14" s="290" t="s">

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10E1A5F5-D99A-4A2F-953E-1CEA964236EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A039970-61F2-45F4-8B43-043236DA2481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="822" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Theo dõi HĐ_Chi tiết" sheetId="2" r:id="rId1"/>
@@ -572,7 +572,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3500" uniqueCount="1302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3490" uniqueCount="1302">
   <si>
     <t>filter</t>
   </si>
@@ -11910,7 +11910,7 @@
       </c>
       <c r="AR41" s="120"/>
     </row>
-    <row r="42" spans="1:44" s="121" customFormat="1" ht="36" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:44" s="121" customFormat="1" ht="24" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
         <v>39</v>
       </c>
@@ -21142,7 +21142,7 @@
       </c>
       <c r="AJ4" s="169">
         <f ca="1">AC4-TODAY()</f>
-        <v>-144</v>
+        <v>-156</v>
       </c>
       <c r="AK4" s="170">
         <f>3*D4</f>
@@ -21279,7 +21279,7 @@
       </c>
       <c r="AJ5" s="179">
         <f ca="1">AD5-TODAY()</f>
-        <v>-109</v>
+        <v>-121</v>
       </c>
       <c r="AK5" s="173">
         <f>3*D5</f>
@@ -21416,7 +21416,7 @@
       </c>
       <c r="AJ6" s="169">
         <f ca="1">AB6-TODAY()</f>
-        <v>-145</v>
+        <v>-157</v>
       </c>
       <c r="AK6" s="170">
         <f>3*D6</f>
@@ -21553,7 +21553,7 @@
       </c>
       <c r="AJ7" s="179">
         <f ca="1">T7-TODAY()</f>
-        <v>-174</v>
+        <v>-186</v>
       </c>
       <c r="AK7" s="173">
         <f>6*D7</f>
@@ -21690,7 +21690,7 @@
       </c>
       <c r="AJ8" s="186">
         <f ca="1">AB8-TODAY()</f>
-        <v>-114</v>
+        <v>-126</v>
       </c>
       <c r="AK8" s="164">
         <f>3*D8</f>
@@ -21827,7 +21827,7 @@
       </c>
       <c r="AJ9" s="169">
         <f ca="1">AB9-TODAY()</f>
-        <v>-130</v>
+        <v>-142</v>
       </c>
       <c r="AK9" s="164">
         <f>3*D9</f>
@@ -21964,7 +21964,7 @@
       </c>
       <c r="AJ10" s="169">
         <f ca="1">AB10-TODAY()</f>
-        <v>-174</v>
+        <v>-186</v>
       </c>
       <c r="AK10" s="164">
         <f>D10*3</f>
@@ -22101,7 +22101,7 @@
       </c>
       <c r="AJ11" s="169">
         <f ca="1">AB11-TODAY()</f>
-        <v>-181</v>
+        <v>-193</v>
       </c>
       <c r="AK11" s="187">
         <f>D11*3</f>
@@ -22238,7 +22238,7 @@
       </c>
       <c r="AJ12" s="169">
         <f ca="1">AA12-TODAY()</f>
-        <v>-174</v>
+        <v>-186</v>
       </c>
       <c r="AK12" s="164">
         <f>3*D12</f>
@@ -22375,7 +22375,7 @@
       </c>
       <c r="AJ13" s="169">
         <f ca="1">AB13-TODAY()</f>
-        <v>-173</v>
+        <v>-185</v>
       </c>
       <c r="AK13" s="164">
         <f>3*7000000</f>
@@ -22512,7 +22512,7 @@
       </c>
       <c r="AJ14" s="186">
         <f ca="1">AA14-TODAY()</f>
-        <v>-164</v>
+        <v>-176</v>
       </c>
       <c r="AK14" s="164">
         <f>3*D14</f>
@@ -22649,7 +22649,7 @@
       </c>
       <c r="AJ15" s="186">
         <f ca="1">T15-TODAY()</f>
-        <v>-33</v>
+        <v>-45</v>
       </c>
       <c r="AK15" s="164">
         <f>6*D15</f>
@@ -22785,7 +22785,7 @@
       </c>
       <c r="AJ16" s="169">
         <f ca="1">T16-TODAY()</f>
-        <v>-120</v>
+        <v>-132</v>
       </c>
       <c r="AK16" s="164">
         <f>6*D16</f>
@@ -22926,7 +22926,7 @@
       </c>
       <c r="AJ17" s="186">
         <f ca="1">AB17-TODAY()</f>
-        <v>-113</v>
+        <v>-125</v>
       </c>
       <c r="AK17" s="164">
         <f>3*D17</f>
@@ -23063,7 +23063,7 @@
       </c>
       <c r="AJ18" s="186">
         <f ca="1">T18-TODAY()</f>
-        <v>-99</v>
+        <v>-111</v>
       </c>
       <c r="AK18" s="164">
         <f>6*D18</f>
@@ -23200,7 +23200,7 @@
       </c>
       <c r="AJ19" s="186">
         <f ca="1">AA19-TODAY()</f>
-        <v>-133</v>
+        <v>-145</v>
       </c>
       <c r="AK19" s="164">
         <f>3*D19</f>
@@ -23337,7 +23337,7 @@
       </c>
       <c r="AJ20" s="192">
         <f ca="1">T20-TODAY()</f>
-        <v>-21</v>
+        <v>-33</v>
       </c>
       <c r="AK20" s="173">
         <f>6*D20</f>
@@ -23474,7 +23474,7 @@
       </c>
       <c r="AJ21" s="186">
         <f ca="1">AB21-TODAY()</f>
-        <v>-109</v>
+        <v>-121</v>
       </c>
       <c r="AK21" s="164">
         <f>3*D21</f>
@@ -23611,7 +23611,7 @@
       </c>
       <c r="AJ22" s="186">
         <f ca="1">T22-TODAY()</f>
-        <v>-45</v>
+        <v>-57</v>
       </c>
       <c r="AK22" s="164">
         <f>6*D22</f>
@@ -23748,7 +23748,7 @@
       </c>
       <c r="AJ23" s="186">
         <f ca="1">T23-TODAY()</f>
-        <v>-45</v>
+        <v>-57</v>
       </c>
       <c r="AK23" s="164">
         <f>D23*6</f>
@@ -23885,7 +23885,7 @@
       </c>
       <c r="AJ24" s="186">
         <f ca="1">Z24-TODAY()</f>
-        <v>-92</v>
+        <v>-104</v>
       </c>
       <c r="AK24" s="187">
         <f>3*D24</f>
@@ -24022,7 +24022,7 @@
       </c>
       <c r="AJ25" s="192">
         <f ca="1">AA25-TODAY()</f>
-        <v>-130</v>
+        <v>-142</v>
       </c>
       <c r="AK25" s="173">
         <f>3*D25</f>
@@ -24159,7 +24159,7 @@
       </c>
       <c r="AJ26" s="186">
         <f ca="1">S26-TODAY()</f>
-        <v>-174</v>
+        <v>-186</v>
       </c>
       <c r="AK26" s="164">
         <f>6*D26</f>
@@ -24296,7 +24296,7 @@
       </c>
       <c r="AJ27" s="186">
         <f ca="1">AA27-TODAY()</f>
-        <v>-144</v>
+        <v>-156</v>
       </c>
       <c r="AK27" s="164">
         <f>3*D27</f>
@@ -24433,7 +24433,7 @@
       </c>
       <c r="AJ28" s="192">
         <f ca="1">T28-TODAY()</f>
-        <v>-98</v>
+        <v>-110</v>
       </c>
       <c r="AK28" s="173">
         <f>6*D28</f>
@@ -24568,7 +24568,7 @@
       </c>
       <c r="AJ29" s="186">
         <f ca="1">U29-TODAY()</f>
-        <v>-83</v>
+        <v>-95</v>
       </c>
       <c r="AK29" s="201">
         <f>D29*6</f>
@@ -24705,7 +24705,7 @@
       </c>
       <c r="AJ30" s="186">
         <f ca="1">Z30-TODAY()</f>
-        <v>-140</v>
+        <v>-152</v>
       </c>
       <c r="AK30" s="201">
         <f>D30*3</f>
@@ -24842,7 +24842,7 @@
       </c>
       <c r="AJ31" s="192">
         <f ca="1">T31-TODAY()</f>
-        <v>-12</v>
+        <v>-24</v>
       </c>
       <c r="AK31" s="194">
         <f>D31*6</f>
@@ -24979,7 +24979,7 @@
       </c>
       <c r="AJ32" s="186">
         <f ca="1">Z32-TODAY()</f>
-        <v>-104</v>
+        <v>-116</v>
       </c>
       <c r="AK32" s="201">
         <f t="shared" ref="AK32:AK36" si="41">D32*3</f>
@@ -25116,7 +25116,7 @@
       </c>
       <c r="AJ33" s="186">
         <f ca="1">Z33-TODAY()</f>
-        <v>-147</v>
+        <v>-159</v>
       </c>
       <c r="AK33" s="205">
         <f t="shared" si="41"/>
@@ -25253,7 +25253,7 @@
       </c>
       <c r="AJ34" s="192">
         <f ca="1">Z34-TODAY()</f>
-        <v>-120</v>
+        <v>-132</v>
       </c>
       <c r="AK34" s="194">
         <f t="shared" si="41"/>
@@ -25390,7 +25390,7 @@
       </c>
       <c r="AJ35" s="186">
         <f ca="1">Z35-TODAY()</f>
-        <v>-114</v>
+        <v>-126</v>
       </c>
       <c r="AK35" s="201">
         <f t="shared" si="41"/>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="AJ36" s="186">
         <f ca="1">Z36-TODAY()</f>
-        <v>-114</v>
+        <v>-126</v>
       </c>
       <c r="AK36" s="201">
         <f t="shared" si="41"/>
@@ -25663,7 +25663,7 @@
       </c>
       <c r="AJ37" s="186">
         <f ca="1">S37-TODAY()</f>
-        <v>-113</v>
+        <v>-125</v>
       </c>
       <c r="AK37" s="201">
         <f>D37*6</f>
@@ -25800,7 +25800,7 @@
       </c>
       <c r="AJ38" s="186">
         <f ca="1">S38-TODAY()</f>
-        <v>-113</v>
+        <v>-125</v>
       </c>
       <c r="AK38" s="201">
         <f>D38*6</f>
@@ -25937,7 +25937,7 @@
       </c>
       <c r="AJ39" s="186">
         <f ca="1">S39-TODAY()</f>
-        <v>-99</v>
+        <v>-111</v>
       </c>
       <c r="AK39" s="201">
         <f>D39*6</f>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ40" s="186">
         <f ca="1">Z40-TODAY()</f>
-        <v>-99</v>
+        <v>-111</v>
       </c>
       <c r="AK40" s="201">
         <f>D40*3</f>
@@ -26211,7 +26211,7 @@
       </c>
       <c r="AJ41" s="186">
         <f ca="1">Y41-TODAY()</f>
-        <v>-181</v>
+        <v>-193</v>
       </c>
       <c r="AK41" s="201">
         <f>D41*3</f>
@@ -26348,7 +26348,7 @@
       </c>
       <c r="AJ42" s="186">
         <f ca="1">X42-TODAY()</f>
-        <v>-144</v>
+        <v>-156</v>
       </c>
       <c r="AK42" s="201">
         <f t="shared" ref="AK42:AK43" si="50">D42*3</f>
@@ -26485,7 +26485,7 @@
       </c>
       <c r="AJ43" s="192">
         <f ca="1">X43-TODAY()</f>
-        <v>-130</v>
+        <v>-142</v>
       </c>
       <c r="AK43" s="194">
         <f t="shared" si="50"/>
@@ -26619,7 +26619,7 @@
       </c>
       <c r="AJ44" s="186">
         <f ca="1">U44-TODAY()</f>
-        <v>-144</v>
+        <v>-156</v>
       </c>
       <c r="AK44" s="201">
         <f>D44*6</f>
@@ -26756,7 +26756,7 @@
       </c>
       <c r="AJ45" s="192">
         <f ca="1">R45-TODAY()</f>
-        <v>-12</v>
+        <v>-24</v>
       </c>
       <c r="AK45" s="194">
         <f>D45*6</f>
@@ -26893,7 +26893,7 @@
       </c>
       <c r="AJ46" s="186">
         <f ca="1">Y46-TODAY()</f>
-        <v>-160</v>
+        <v>-172</v>
       </c>
       <c r="AK46" s="201">
         <f>D46*1</f>
@@ -27030,7 +27030,7 @@
       </c>
       <c r="AJ47" s="186">
         <f ca="1">R47-TODAY()</f>
-        <v>-38</v>
+        <v>-50</v>
       </c>
       <c r="AK47" s="201">
         <v>24000000</v>
@@ -27170,7 +27170,7 @@
       </c>
       <c r="AJ48" s="186">
         <f ca="1">R48-TODAY()</f>
-        <v>-38</v>
+        <v>-50</v>
       </c>
       <c r="AK48" s="201">
         <v>24000000</v>
@@ -27306,7 +27306,7 @@
       </c>
       <c r="AJ49" s="186">
         <f ca="1">R49-TODAY()</f>
-        <v>-22</v>
+        <v>-34</v>
       </c>
       <c r="AK49" s="201">
         <f>D49*6</f>
@@ -27443,7 +27443,7 @@
       </c>
       <c r="AJ50" s="186">
         <f t="shared" ref="AJ50:AJ54" ca="1" si="57">Q50-TODAY()</f>
-        <v>-144</v>
+        <v>-156</v>
       </c>
       <c r="AK50" s="201">
         <f>D50*6</f>
@@ -27580,7 +27580,7 @@
       </c>
       <c r="AJ51" s="186">
         <f t="shared" ca="1" si="57"/>
-        <v>-62</v>
+        <v>-74</v>
       </c>
       <c r="AK51" s="194">
         <f t="shared" ref="AK51:AK60" si="58">D51*6</f>
@@ -27717,7 +27717,7 @@
       </c>
       <c r="AJ52" s="186">
         <f t="shared" ca="1" si="57"/>
-        <v>-83</v>
+        <v>-95</v>
       </c>
       <c r="AK52" s="201">
         <f>D52*6</f>
@@ -27854,7 +27854,7 @@
       </c>
       <c r="AJ53" s="186">
         <f t="shared" ca="1" si="57"/>
-        <v>-87</v>
+        <v>-99</v>
       </c>
       <c r="AK53" s="201">
         <f t="shared" si="58"/>
@@ -27991,7 +27991,7 @@
       </c>
       <c r="AJ54" s="186">
         <f t="shared" ca="1" si="57"/>
-        <v>-88</v>
+        <v>-100</v>
       </c>
       <c r="AK54" s="201">
         <f t="shared" si="58"/>
@@ -28128,7 +28128,7 @@
       </c>
       <c r="AJ55" s="186">
         <f ca="1">R55-TODAY()</f>
-        <v>-52</v>
+        <v>-64</v>
       </c>
       <c r="AK55" s="201">
         <f t="shared" si="58"/>
@@ -28265,7 +28265,7 @@
       </c>
       <c r="AJ56" s="186">
         <f t="shared" ref="AJ56:AJ67" ca="1" si="60">P56-TODAY()</f>
-        <v>-178</v>
+        <v>-190</v>
       </c>
       <c r="AK56" s="201">
         <f t="shared" si="58"/>
@@ -28402,7 +28402,7 @@
       </c>
       <c r="AJ57" s="186">
         <f t="shared" ca="1" si="60"/>
-        <v>-165</v>
+        <v>-177</v>
       </c>
       <c r="AK57" s="201">
         <f t="shared" si="58"/>
@@ -28539,7 +28539,7 @@
       </c>
       <c r="AJ58" s="186">
         <f ca="1">Q58-TODAY()</f>
-        <v>-17</v>
+        <v>-29</v>
       </c>
       <c r="AK58" s="201">
         <f t="shared" si="58"/>
@@ -28676,7 +28676,7 @@
       </c>
       <c r="AJ59" s="186">
         <f t="shared" ca="1" si="60"/>
-        <v>-144</v>
+        <v>-156</v>
       </c>
       <c r="AK59" s="201">
         <f t="shared" si="58"/>
@@ -28813,7 +28813,7 @@
       </c>
       <c r="AJ60" s="186">
         <f t="shared" ca="1" si="60"/>
-        <v>-144</v>
+        <v>-156</v>
       </c>
       <c r="AK60" s="201">
         <f t="shared" si="58"/>
@@ -28950,7 +28950,7 @@
       </c>
       <c r="AJ61" s="186">
         <f t="shared" ca="1" si="60"/>
-        <v>-153</v>
+        <v>-165</v>
       </c>
       <c r="AK61" s="201">
         <f>D61*6</f>
@@ -29087,7 +29087,7 @@
       </c>
       <c r="AJ62" s="186">
         <f t="shared" ca="1" si="60"/>
-        <v>-108</v>
+        <v>-120</v>
       </c>
       <c r="AK62" s="201">
         <f t="shared" ref="AK62:AK85" si="63">D62*6</f>
@@ -29224,7 +29224,7 @@
       </c>
       <c r="AJ63" s="186">
         <f t="shared" ca="1" si="60"/>
-        <v>-99</v>
+        <v>-111</v>
       </c>
       <c r="AK63" s="201">
         <f t="shared" si="63"/>
@@ -29361,7 +29361,7 @@
       </c>
       <c r="AJ64" s="186">
         <f t="shared" ca="1" si="60"/>
-        <v>-104</v>
+        <v>-116</v>
       </c>
       <c r="AK64" s="201">
         <f>D64*6</f>
@@ -29498,7 +29498,7 @@
       </c>
       <c r="AJ65" s="186">
         <f t="shared" ca="1" si="60"/>
-        <v>-94</v>
+        <v>-106</v>
       </c>
       <c r="AK65" s="201">
         <f t="shared" si="63"/>
@@ -29635,7 +29635,7 @@
       </c>
       <c r="AJ66" s="186">
         <f t="shared" ca="1" si="60"/>
-        <v>-74</v>
+        <v>-86</v>
       </c>
       <c r="AK66" s="201">
         <f>D66*6</f>
@@ -29772,7 +29772,7 @@
       </c>
       <c r="AJ67" s="186">
         <f t="shared" ca="1" si="60"/>
-        <v>-66</v>
+        <v>-78</v>
       </c>
       <c r="AK67" s="201">
         <f t="shared" si="63"/>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="AJ68" s="186">
         <f ca="1">P68-TODAY()</f>
-        <v>-12</v>
+        <v>-24</v>
       </c>
       <c r="AK68" s="201">
         <f t="shared" si="63"/>
@@ -30049,7 +30049,7 @@
       </c>
       <c r="AJ69" s="186">
         <f ca="1">P69-TODAY()</f>
-        <v>-21</v>
+        <v>-33</v>
       </c>
       <c r="AK69" s="201">
         <f t="shared" si="63"/>
@@ -30186,7 +30186,7 @@
       </c>
       <c r="AJ70" s="186">
         <f t="shared" ref="AJ70:AJ73" ca="1" si="66">O70-TODAY()</f>
-        <v>-157</v>
+        <v>-169</v>
       </c>
       <c r="AK70" s="201">
         <f t="shared" si="63"/>
@@ -30323,7 +30323,7 @@
       </c>
       <c r="AJ71" s="186">
         <f ca="1">P71-TODAY()</f>
-        <v>-27</v>
+        <v>-39</v>
       </c>
       <c r="AK71" s="201">
         <f t="shared" si="63"/>
@@ -30460,7 +30460,7 @@
       </c>
       <c r="AJ72" s="186">
         <f t="shared" ca="1" si="66"/>
-        <v>-119</v>
+        <v>-131</v>
       </c>
       <c r="AK72" s="201">
         <f t="shared" si="63"/>
@@ -30597,7 +30597,7 @@
       </c>
       <c r="AJ73" s="186">
         <f t="shared" ca="1" si="66"/>
-        <v>-101</v>
+        <v>-113</v>
       </c>
       <c r="AK73" s="201">
         <f t="shared" si="63"/>
@@ -30734,7 +30734,7 @@
       </c>
       <c r="AJ74" s="186">
         <f ca="1">O74-TODAY()</f>
-        <v>-64</v>
+        <v>-76</v>
       </c>
       <c r="AK74" s="201">
         <f t="shared" si="63"/>
@@ -30871,7 +30871,7 @@
       </c>
       <c r="AJ75" s="186">
         <f ca="1">O75-TODAY()</f>
-        <v>-58</v>
+        <v>-70</v>
       </c>
       <c r="AK75" s="201">
         <f t="shared" si="63"/>
@@ -31008,7 +31008,7 @@
       </c>
       <c r="AJ76" s="186">
         <f ca="1">O76-TODAY()</f>
-        <v>-66</v>
+        <v>-78</v>
       </c>
       <c r="AK76" s="201">
         <f t="shared" si="63"/>
@@ -31145,7 +31145,7 @@
       </c>
       <c r="AJ77" s="186">
         <f ca="1">O77-TODAY()</f>
-        <v>-36</v>
+        <v>-48</v>
       </c>
       <c r="AK77" s="201">
         <f t="shared" si="63"/>
@@ -31286,7 +31286,7 @@
       </c>
       <c r="AJ78" s="186">
         <f t="shared" ref="AJ78:AJ79" ca="1" si="67">N78-TODAY()</f>
-        <v>-123</v>
+        <v>-135</v>
       </c>
       <c r="AK78" s="201">
         <f t="shared" si="63"/>
@@ -31423,7 +31423,7 @@
       </c>
       <c r="AJ79" s="186">
         <f t="shared" ca="1" si="67"/>
-        <v>-118</v>
+        <v>-130</v>
       </c>
       <c r="AK79" s="201">
         <f t="shared" si="63"/>
@@ -31560,7 +31560,7 @@
       </c>
       <c r="AJ80" s="186">
         <f ca="1">N80-TODAY()</f>
-        <v>-65</v>
+        <v>-77</v>
       </c>
       <c r="AK80" s="201">
         <f t="shared" si="63"/>
@@ -31697,7 +31697,7 @@
       </c>
       <c r="AJ81" s="186">
         <f ca="1">N81-TODAY()</f>
-        <v>-52</v>
+        <v>-64</v>
       </c>
       <c r="AK81" s="201">
         <f t="shared" si="63"/>
@@ -31834,7 +31834,7 @@
       </c>
       <c r="AJ82" s="186">
         <f ca="1">N82-TODAY()</f>
-        <v>-76</v>
+        <v>-88</v>
       </c>
       <c r="AK82" s="201">
         <f t="shared" si="63"/>
@@ -31971,7 +31971,7 @@
       </c>
       <c r="AJ83" s="186">
         <f ca="1">N83-TODAY()</f>
-        <v>-75</v>
+        <v>-87</v>
       </c>
       <c r="AK83" s="201">
         <f t="shared" si="63"/>
@@ -32108,7 +32108,7 @@
       </c>
       <c r="AJ84" s="186">
         <f ca="1">N84-TODAY()</f>
-        <v>-17</v>
+        <v>-29</v>
       </c>
       <c r="AK84" s="201">
         <f t="shared" si="63"/>
@@ -32245,7 +32245,7 @@
       </c>
       <c r="AJ85" s="186">
         <f ca="1">M85-TODAY()</f>
-        <v>-174</v>
+        <v>-186</v>
       </c>
       <c r="AK85" s="201">
         <f t="shared" si="63"/>
@@ -42158,6 +42158,7 @@
     <col min="6" max="6" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.44140625" customWidth="1"/>
     <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="12.21875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -42296,91 +42297,91 @@
       </c>
       <c r="K2" s="223">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="L2" s="223">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="M2" s="223">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="N2" s="223">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="O2" s="223">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="P2" s="223">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Q2" s="223">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="R2" s="223">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="S2" s="223">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T2" s="223">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="U2" s="223">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="V2" s="223">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="W2" s="223">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="X2" s="223">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Y2" s="223">
         <f t="shared" ref="Y2:AB2" si="2">SUBTOTAL(3,Y4:Y50)</f>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Z2" s="223">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AA2" s="223">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AB2" s="223">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AC2" s="223">
         <f t="shared" ref="AC2:AE2" si="3">SUBTOTAL(3,AC4:AC50)</f>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AD2" s="223">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AE2" s="223">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AF2" s="247">
         <f>SUBTOTAL(9,AF4:AF50)</f>
-        <v>233673000</v>
+        <v>322024200</v>
       </c>
       <c r="AG2" s="17"/>
     </row>
@@ -42508,7 +42509,7 @@
         <v>44774</v>
       </c>
       <c r="J4" s="249">
-        <f t="shared" ref="J4:X12" si="4">EDATE(I4,3)</f>
+        <f t="shared" ref="J4:X13" si="4">EDATE(I4,3)</f>
         <v>44866</v>
       </c>
       <c r="K4" s="249">
@@ -42876,7 +42877,7 @@
         <v>44896</v>
       </c>
       <c r="J7" s="249">
-        <f t="shared" ref="J7:K12" si="11">EDATE(I7,3)</f>
+        <f t="shared" ref="J7:K13" si="11">EDATE(I7,3)</f>
         <v>44986</v>
       </c>
       <c r="K7" s="249">
@@ -43302,7 +43303,7 @@
         <v>46235</v>
       </c>
       <c r="Y10" s="249">
-        <f t="shared" ref="Y10:AB12" si="15">EDATE(X10,3)</f>
+        <f t="shared" ref="Y10:AB13" si="15">EDATE(X10,3)</f>
         <v>46327</v>
       </c>
       <c r="Z10" s="249">
@@ -43454,7 +43455,7 @@
         <v>47574</v>
       </c>
       <c r="AF11" s="227">
-        <f t="shared" ref="AF11:AF12" si="18">F11*3</f>
+        <f t="shared" ref="AF11:AF13" si="18">F11*3</f>
         <v>18150000</v>
       </c>
       <c r="AG11" s="17"/>
@@ -43564,7 +43565,7 @@
         <v>47300</v>
       </c>
       <c r="AC12" s="249">
-        <f t="shared" ref="AC12:AE12" si="19">EDATE(AB12,3)</f>
+        <f t="shared" ref="AC12:AE13" si="19">EDATE(AB12,3)</f>
         <v>47392</v>
       </c>
       <c r="AD12" s="249">
@@ -43606,11 +43607,100 @@
       <c r="H13" s="292">
         <v>46107</v>
       </c>
-      <c r="I13" s="293" t="s">
-        <v>777</v>
-      </c>
-      <c r="J13" s="293" t="s">
-        <v>777</v>
+      <c r="I13" s="293">
+        <v>46296</v>
+      </c>
+      <c r="J13" s="249">
+        <f t="shared" si="11"/>
+        <v>46388</v>
+      </c>
+      <c r="K13" s="249">
+        <f t="shared" ref="K13" si="20">EDATE(J13,3)</f>
+        <v>46478</v>
+      </c>
+      <c r="L13" s="249">
+        <f t="shared" si="4"/>
+        <v>46569</v>
+      </c>
+      <c r="M13" s="249">
+        <f t="shared" si="4"/>
+        <v>46661</v>
+      </c>
+      <c r="N13" s="249">
+        <f t="shared" si="4"/>
+        <v>46753</v>
+      </c>
+      <c r="O13" s="249">
+        <f t="shared" si="4"/>
+        <v>46844</v>
+      </c>
+      <c r="P13" s="249">
+        <f t="shared" si="4"/>
+        <v>46935</v>
+      </c>
+      <c r="Q13" s="249">
+        <f t="shared" si="4"/>
+        <v>47027</v>
+      </c>
+      <c r="R13" s="249">
+        <f t="shared" si="4"/>
+        <v>47119</v>
+      </c>
+      <c r="S13" s="249">
+        <f t="shared" si="4"/>
+        <v>47209</v>
+      </c>
+      <c r="T13" s="249">
+        <f t="shared" si="4"/>
+        <v>47300</v>
+      </c>
+      <c r="U13" s="249">
+        <f t="shared" si="4"/>
+        <v>47392</v>
+      </c>
+      <c r="V13" s="249">
+        <f t="shared" si="4"/>
+        <v>47484</v>
+      </c>
+      <c r="W13" s="249">
+        <f t="shared" si="4"/>
+        <v>47574</v>
+      </c>
+      <c r="X13" s="249">
+        <f t="shared" si="4"/>
+        <v>47665</v>
+      </c>
+      <c r="Y13" s="249">
+        <f t="shared" si="15"/>
+        <v>47757</v>
+      </c>
+      <c r="Z13" s="249">
+        <f t="shared" si="15"/>
+        <v>47849</v>
+      </c>
+      <c r="AA13" s="249">
+        <f t="shared" si="15"/>
+        <v>47939</v>
+      </c>
+      <c r="AB13" s="249">
+        <f t="shared" si="15"/>
+        <v>48030</v>
+      </c>
+      <c r="AC13" s="249">
+        <f t="shared" si="19"/>
+        <v>48122</v>
+      </c>
+      <c r="AD13" s="249">
+        <f t="shared" si="19"/>
+        <v>48214</v>
+      </c>
+      <c r="AE13" s="249">
+        <f t="shared" si="19"/>
+        <v>48305</v>
+      </c>
+      <c r="AF13" s="227">
+        <f t="shared" si="18"/>
+        <v>17490000</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.3">
@@ -43702,14 +43792,103 @@
       <c r="H16" s="292">
         <v>46107</v>
       </c>
-      <c r="I16" s="293" t="s">
-        <v>777</v>
-      </c>
-      <c r="J16" s="293" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I16" s="293">
+        <v>46296</v>
+      </c>
+      <c r="J16" s="249">
+        <f t="shared" ref="J16" si="21">EDATE(I16,3)</f>
+        <v>46388</v>
+      </c>
+      <c r="K16" s="249">
+        <f t="shared" ref="K16:K19" si="22">EDATE(J16,3)</f>
+        <v>46478</v>
+      </c>
+      <c r="L16" s="249">
+        <f t="shared" ref="L16:L19" si="23">EDATE(K16,3)</f>
+        <v>46569</v>
+      </c>
+      <c r="M16" s="249">
+        <f t="shared" ref="M16:M19" si="24">EDATE(L16,3)</f>
+        <v>46661</v>
+      </c>
+      <c r="N16" s="249">
+        <f t="shared" ref="N16:N19" si="25">EDATE(M16,3)</f>
+        <v>46753</v>
+      </c>
+      <c r="O16" s="249">
+        <f t="shared" ref="O16:O19" si="26">EDATE(N16,3)</f>
+        <v>46844</v>
+      </c>
+      <c r="P16" s="249">
+        <f t="shared" ref="P16:P19" si="27">EDATE(O16,3)</f>
+        <v>46935</v>
+      </c>
+      <c r="Q16" s="249">
+        <f t="shared" ref="Q16:Q19" si="28">EDATE(P16,3)</f>
+        <v>47027</v>
+      </c>
+      <c r="R16" s="249">
+        <f t="shared" ref="R16:R19" si="29">EDATE(Q16,3)</f>
+        <v>47119</v>
+      </c>
+      <c r="S16" s="249">
+        <f t="shared" ref="S16:S19" si="30">EDATE(R16,3)</f>
+        <v>47209</v>
+      </c>
+      <c r="T16" s="249">
+        <f t="shared" ref="T16:T19" si="31">EDATE(S16,3)</f>
+        <v>47300</v>
+      </c>
+      <c r="U16" s="249">
+        <f t="shared" ref="U16:U19" si="32">EDATE(T16,3)</f>
+        <v>47392</v>
+      </c>
+      <c r="V16" s="249">
+        <f t="shared" ref="V16:V19" si="33">EDATE(U16,3)</f>
+        <v>47484</v>
+      </c>
+      <c r="W16" s="249">
+        <f t="shared" ref="W16:W19" si="34">EDATE(V16,3)</f>
+        <v>47574</v>
+      </c>
+      <c r="X16" s="249">
+        <f t="shared" ref="X16:X19" si="35">EDATE(W16,3)</f>
+        <v>47665</v>
+      </c>
+      <c r="Y16" s="249">
+        <f t="shared" ref="Y16:Y19" si="36">EDATE(X16,3)</f>
+        <v>47757</v>
+      </c>
+      <c r="Z16" s="249">
+        <f t="shared" ref="Z16:Z19" si="37">EDATE(Y16,3)</f>
+        <v>47849</v>
+      </c>
+      <c r="AA16" s="249">
+        <f t="shared" ref="AA16:AA19" si="38">EDATE(Z16,3)</f>
+        <v>47939</v>
+      </c>
+      <c r="AB16" s="249">
+        <f t="shared" ref="AB16:AB19" si="39">EDATE(AA16,3)</f>
+        <v>48030</v>
+      </c>
+      <c r="AC16" s="249">
+        <f t="shared" ref="AC16:AC19" si="40">EDATE(AB16,3)</f>
+        <v>48122</v>
+      </c>
+      <c r="AD16" s="249">
+        <f t="shared" ref="AD16:AD19" si="41">EDATE(AC16,3)</f>
+        <v>48214</v>
+      </c>
+      <c r="AE16" s="249">
+        <f t="shared" ref="AE16:AE19" si="42">EDATE(AD16,3)</f>
+        <v>48305</v>
+      </c>
+      <c r="AF16" s="227">
+        <f t="shared" ref="AF16:AF19" si="43">F16*3</f>
+        <v>19500000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A17" s="224">
         <v>14</v>
       </c>
@@ -43734,14 +43913,103 @@
       <c r="H17" s="292">
         <v>46108</v>
       </c>
-      <c r="I17" s="293" t="s">
-        <v>777</v>
-      </c>
-      <c r="J17" s="293" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I17" s="293">
+        <v>46296</v>
+      </c>
+      <c r="J17" s="249">
+        <f t="shared" ref="J17:J18" si="44">EDATE(I17,3)</f>
+        <v>46388</v>
+      </c>
+      <c r="K17" s="249">
+        <f t="shared" si="22"/>
+        <v>46478</v>
+      </c>
+      <c r="L17" s="249">
+        <f t="shared" si="23"/>
+        <v>46569</v>
+      </c>
+      <c r="M17" s="249">
+        <f t="shared" si="24"/>
+        <v>46661</v>
+      </c>
+      <c r="N17" s="249">
+        <f t="shared" si="25"/>
+        <v>46753</v>
+      </c>
+      <c r="O17" s="249">
+        <f t="shared" si="26"/>
+        <v>46844</v>
+      </c>
+      <c r="P17" s="249">
+        <f t="shared" si="27"/>
+        <v>46935</v>
+      </c>
+      <c r="Q17" s="249">
+        <f t="shared" si="28"/>
+        <v>47027</v>
+      </c>
+      <c r="R17" s="249">
+        <f t="shared" si="29"/>
+        <v>47119</v>
+      </c>
+      <c r="S17" s="249">
+        <f t="shared" si="30"/>
+        <v>47209</v>
+      </c>
+      <c r="T17" s="249">
+        <f t="shared" si="31"/>
+        <v>47300</v>
+      </c>
+      <c r="U17" s="249">
+        <f t="shared" si="32"/>
+        <v>47392</v>
+      </c>
+      <c r="V17" s="249">
+        <f t="shared" si="33"/>
+        <v>47484</v>
+      </c>
+      <c r="W17" s="249">
+        <f t="shared" si="34"/>
+        <v>47574</v>
+      </c>
+      <c r="X17" s="249">
+        <f t="shared" si="35"/>
+        <v>47665</v>
+      </c>
+      <c r="Y17" s="249">
+        <f t="shared" si="36"/>
+        <v>47757</v>
+      </c>
+      <c r="Z17" s="249">
+        <f t="shared" si="37"/>
+        <v>47849</v>
+      </c>
+      <c r="AA17" s="249">
+        <f t="shared" si="38"/>
+        <v>47939</v>
+      </c>
+      <c r="AB17" s="249">
+        <f t="shared" si="39"/>
+        <v>48030</v>
+      </c>
+      <c r="AC17" s="249">
+        <f t="shared" si="40"/>
+        <v>48122</v>
+      </c>
+      <c r="AD17" s="249">
+        <f t="shared" si="41"/>
+        <v>48214</v>
+      </c>
+      <c r="AE17" s="249">
+        <f t="shared" si="42"/>
+        <v>48305</v>
+      </c>
+      <c r="AF17" s="227">
+        <f t="shared" si="43"/>
+        <v>19800000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A18" s="224">
         <v>15</v>
       </c>
@@ -43766,14 +44034,103 @@
       <c r="H18" s="292">
         <v>46010</v>
       </c>
-      <c r="I18" s="293" t="s">
-        <v>777</v>
-      </c>
-      <c r="J18" s="293" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I18" s="293">
+        <v>46357</v>
+      </c>
+      <c r="J18" s="249">
+        <f t="shared" si="44"/>
+        <v>46447</v>
+      </c>
+      <c r="K18" s="249">
+        <f t="shared" si="22"/>
+        <v>46539</v>
+      </c>
+      <c r="L18" s="249">
+        <f t="shared" si="23"/>
+        <v>46631</v>
+      </c>
+      <c r="M18" s="249">
+        <f t="shared" si="24"/>
+        <v>46722</v>
+      </c>
+      <c r="N18" s="249">
+        <f t="shared" si="25"/>
+        <v>46813</v>
+      </c>
+      <c r="O18" s="249">
+        <f t="shared" si="26"/>
+        <v>46905</v>
+      </c>
+      <c r="P18" s="249">
+        <f t="shared" si="27"/>
+        <v>46997</v>
+      </c>
+      <c r="Q18" s="249">
+        <f t="shared" si="28"/>
+        <v>47088</v>
+      </c>
+      <c r="R18" s="249">
+        <f t="shared" si="29"/>
+        <v>47178</v>
+      </c>
+      <c r="S18" s="249">
+        <f t="shared" si="30"/>
+        <v>47270</v>
+      </c>
+      <c r="T18" s="249">
+        <f t="shared" si="31"/>
+        <v>47362</v>
+      </c>
+      <c r="U18" s="249">
+        <f t="shared" si="32"/>
+        <v>47453</v>
+      </c>
+      <c r="V18" s="249">
+        <f t="shared" si="33"/>
+        <v>47543</v>
+      </c>
+      <c r="W18" s="249">
+        <f t="shared" si="34"/>
+        <v>47635</v>
+      </c>
+      <c r="X18" s="249">
+        <f t="shared" si="35"/>
+        <v>47727</v>
+      </c>
+      <c r="Y18" s="249">
+        <f t="shared" si="36"/>
+        <v>47818</v>
+      </c>
+      <c r="Z18" s="249">
+        <f t="shared" si="37"/>
+        <v>47908</v>
+      </c>
+      <c r="AA18" s="249">
+        <f t="shared" si="38"/>
+        <v>48000</v>
+      </c>
+      <c r="AB18" s="249">
+        <f t="shared" si="39"/>
+        <v>48092</v>
+      </c>
+      <c r="AC18" s="249">
+        <f t="shared" si="40"/>
+        <v>48183</v>
+      </c>
+      <c r="AD18" s="249">
+        <f t="shared" si="41"/>
+        <v>48274</v>
+      </c>
+      <c r="AE18" s="249">
+        <f t="shared" si="42"/>
+        <v>48366</v>
+      </c>
+      <c r="AF18" s="227">
+        <f t="shared" si="43"/>
+        <v>16731000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A19" s="224">
         <v>16</v>
       </c>
@@ -43798,14 +44155,103 @@
       <c r="H19" s="292">
         <v>46010</v>
       </c>
-      <c r="I19" s="293" t="s">
-        <v>777</v>
-      </c>
-      <c r="J19" s="293" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I19" s="293">
+        <v>46357</v>
+      </c>
+      <c r="J19" s="249">
+        <f t="shared" ref="J19" si="45">EDATE(I19,3)</f>
+        <v>46447</v>
+      </c>
+      <c r="K19" s="249">
+        <f t="shared" si="22"/>
+        <v>46539</v>
+      </c>
+      <c r="L19" s="249">
+        <f t="shared" si="23"/>
+        <v>46631</v>
+      </c>
+      <c r="M19" s="249">
+        <f t="shared" si="24"/>
+        <v>46722</v>
+      </c>
+      <c r="N19" s="249">
+        <f t="shared" si="25"/>
+        <v>46813</v>
+      </c>
+      <c r="O19" s="249">
+        <f t="shared" si="26"/>
+        <v>46905</v>
+      </c>
+      <c r="P19" s="249">
+        <f t="shared" si="27"/>
+        <v>46997</v>
+      </c>
+      <c r="Q19" s="249">
+        <f t="shared" si="28"/>
+        <v>47088</v>
+      </c>
+      <c r="R19" s="249">
+        <f t="shared" si="29"/>
+        <v>47178</v>
+      </c>
+      <c r="S19" s="249">
+        <f t="shared" si="30"/>
+        <v>47270</v>
+      </c>
+      <c r="T19" s="249">
+        <f t="shared" si="31"/>
+        <v>47362</v>
+      </c>
+      <c r="U19" s="249">
+        <f t="shared" si="32"/>
+        <v>47453</v>
+      </c>
+      <c r="V19" s="249">
+        <f t="shared" si="33"/>
+        <v>47543</v>
+      </c>
+      <c r="W19" s="249">
+        <f t="shared" si="34"/>
+        <v>47635</v>
+      </c>
+      <c r="X19" s="249">
+        <f t="shared" si="35"/>
+        <v>47727</v>
+      </c>
+      <c r="Y19" s="249">
+        <f t="shared" si="36"/>
+        <v>47818</v>
+      </c>
+      <c r="Z19" s="249">
+        <f t="shared" si="37"/>
+        <v>47908</v>
+      </c>
+      <c r="AA19" s="249">
+        <f t="shared" si="38"/>
+        <v>48000</v>
+      </c>
+      <c r="AB19" s="249">
+        <f t="shared" si="39"/>
+        <v>48092</v>
+      </c>
+      <c r="AC19" s="249">
+        <f t="shared" si="40"/>
+        <v>48183</v>
+      </c>
+      <c r="AD19" s="249">
+        <f t="shared" si="41"/>
+        <v>48274</v>
+      </c>
+      <c r="AE19" s="249">
+        <f t="shared" si="42"/>
+        <v>48366</v>
+      </c>
+      <c r="AF19" s="227">
+        <f t="shared" si="43"/>
+        <v>14830200</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A20" s="224">
         <v>17</v>
       </c>
@@ -43837,7 +44283,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A21" s="224">
         <v>18</v>
       </c>
@@ -43869,7 +44315,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A22" s="224">
         <v>19</v>
       </c>
